--- a/src/attributions/attributions_ig_traj_54.xlsx
+++ b/src/attributions/attributions_ig_traj_54.xlsx
@@ -999,10 +999,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.04068462286642784</v>
+        <v>0.02768269432123413</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -1011,7 +1011,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.001977714581374433</v>
+        <v>-0.009945015134988154</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -1023,22 +1023,22 @@
         <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02458967762211826</v>
+        <v>0.008261571159499253</v>
       </c>
       <c r="J2" t="n">
         <v>-0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.03817801366000256</v>
+        <v>0.08329373540789138</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.05407369097572671</v>
+        <v>-0.02460116292137465</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -1047,16 +1047,16 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.02074211198254716</v>
+        <v>-0.001292790182118433</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.004365700734343616</v>
+        <v>-0.007361729887463494</v>
       </c>
       <c r="U2" t="n">
         <v>-0</v>
@@ -1065,34 +1065,34 @@
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>-0.006388782460108862</v>
+        <v>-0.02467129286958387</v>
       </c>
       <c r="X2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.0004704875847460587</v>
+        <v>0.0003462569092880659</v>
       </c>
       <c r="AB2" t="n">
         <v>-0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.0372177311581979</v>
+        <v>-0.03112587441113865</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.0371610804789622</v>
+        <v>-0.02950910515727578</v>
       </c>
       <c r="AG2" t="n">
         <v>0</v>
@@ -1101,16 +1101,16 @@
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.01371494386957449</v>
+        <v>0.0004728333635439818</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.01251572400674541</v>
+        <v>0.0150894027454703</v>
       </c>
       <c r="AM2" t="n">
         <v>0</v>
@@ -1119,34 +1119,34 @@
         <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>-0.01229188561375164</v>
+        <v>-0.007106642678100626</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>-0.009443187704772968</v>
+        <v>-0.006932247308849381</v>
       </c>
       <c r="AT2" t="n">
         <v>-0</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.1867043559337945</v>
+        <v>0.119394134891548</v>
       </c>
       <c r="AV2" t="n">
         <v>-0</v>
       </c>
       <c r="AW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.1003186805143905</v>
+        <v>-0.02450368020801672</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
@@ -1158,94 +1158,94 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.009527250400959626</v>
+        <v>0.01610323235104107</v>
       </c>
       <c r="BC2" t="n">
         <v>0</v>
       </c>
       <c r="BD2" t="n">
-        <v>-0.01477088685588362</v>
+        <v>-0.008026923831931848</v>
       </c>
       <c r="BE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BF2" t="n">
         <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>-0.04600800592480059</v>
+        <v>-0.01889005413191675</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.005344153758633155</v>
+        <v>0.002901174642031363</v>
       </c>
       <c r="BL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.01791060559933661</v>
+        <v>0.01958551259696554</v>
       </c>
       <c r="BN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.0909356373935107</v>
+        <v>0.03681301763409359</v>
       </c>
       <c r="BQ2" t="n">
         <v>-0</v>
       </c>
       <c r="BR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
         <v>-0</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.03356307413969204</v>
+        <v>0.01784216449094446</v>
       </c>
       <c r="BU2" t="n">
         <v>-0</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.09142767431139875</v>
+        <v>0.06630563400135431</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.01762217195693348</v>
+        <v>-0.02189455003025409</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB2" t="n">
         <v>0</v>
       </c>
       <c r="CC2" t="n">
-        <v>0.01457290762793991</v>
+        <v>-0.01404921025045271</v>
       </c>
       <c r="CD2" t="n">
         <v>-0</v>
       </c>
       <c r="CE2" t="n">
-        <v>-0.0193109557432488</v>
+        <v>-0.02521534044071978</v>
       </c>
       <c r="CF2" t="n">
         <v>-0</v>
@@ -1254,10 +1254,10 @@
         <v>-0</v>
       </c>
       <c r="CH2" t="n">
-        <v>-0.002301461732836441</v>
+        <v>0.008089655654438258</v>
       </c>
       <c r="CI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ2" t="n">
         <v>-0</v>
@@ -1266,13 +1266,13 @@
         <v>0</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.02771095992752531</v>
+        <v>0.01305874021051265</v>
       </c>
       <c r="CM2" t="n">
         <v>0</v>
       </c>
       <c r="CN2" t="n">
-        <v>-0.007820986863587733</v>
+        <v>-0.01067606279855269</v>
       </c>
       <c r="CO2" t="n">
         <v>-0</v>
@@ -1281,10 +1281,10 @@
         <v>-0</v>
       </c>
       <c r="CQ2" t="n">
-        <v>-0.005010422939580554</v>
+        <v>0.003401270331303097</v>
       </c>
       <c r="CR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS2" t="n">
         <v>-0</v>
@@ -1293,40 +1293,40 @@
         <v>-0</v>
       </c>
       <c r="CU2" t="n">
-        <v>-0.0001031531894095584</v>
+        <v>0.006562369289594585</v>
       </c>
       <c r="CV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW2" t="n">
-        <v>-0.01584225064594657</v>
+        <v>-0.02711170362048707</v>
       </c>
       <c r="CX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY2" t="n">
         <v>0</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.00497114547909328</v>
+        <v>0.003341938059086295</v>
       </c>
       <c r="DA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB2" t="n">
         <v>0</v>
       </c>
       <c r="DC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.02897201632658218</v>
+        <v>0.01195894511088931</v>
       </c>
       <c r="DE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>-0.07815818326522309</v>
+        <v>-0.02132493899602225</v>
       </c>
       <c r="DG2" t="n">
         <v>-0</v>
@@ -1335,7 +1335,7 @@
         <v>-0</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.01734196008038872</v>
+        <v>0.0002630723318953812</v>
       </c>
       <c r="DJ2" t="n">
         <v>-0</v>
@@ -1347,94 +1347,94 @@
         <v>0</v>
       </c>
       <c r="DM2" t="n">
-        <v>-0.01906146803921586</v>
+        <v>-0.006147486570441072</v>
       </c>
       <c r="DN2" t="n">
         <v>-0</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.002706025385042098</v>
+        <v>-0.0156369210696829</v>
       </c>
       <c r="DP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR2" t="n">
-        <v>2.382691148078454e-05</v>
+        <v>0.01406556394266962</v>
       </c>
       <c r="DS2" t="n">
         <v>-0</v>
       </c>
       <c r="DT2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU2" t="n">
         <v>-0</v>
       </c>
       <c r="DV2" t="n">
-        <v>0.009074998968978338</v>
+        <v>-0.0331622268690431</v>
       </c>
       <c r="DW2" t="n">
         <v>-0</v>
       </c>
       <c r="DX2" t="n">
-        <v>-0.009255938460678631</v>
+        <v>0.0182843605054739</v>
       </c>
       <c r="DY2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA2" t="n">
-        <v>-0.0183000320877825</v>
+        <v>-0.01539374411161986</v>
       </c>
       <c r="EB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC2" t="n">
         <v>-0</v>
       </c>
       <c r="ED2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE2" t="n">
-        <v>-0.003259061105714203</v>
+        <v>0.007572507041307319</v>
       </c>
       <c r="EF2" t="n">
         <v>0</v>
       </c>
       <c r="EG2" t="n">
-        <v>-0.001273525481921378</v>
+        <v>-0.02239956146574927</v>
       </c>
       <c r="EH2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.02150072223211565</v>
+        <v>-0.002773417676188482</v>
       </c>
       <c r="EK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM2" t="n">
         <v>0</v>
       </c>
       <c r="EN2" t="n">
-        <v>0.02897942300068863</v>
+        <v>0.006811360347912849</v>
       </c>
       <c r="EO2" t="n">
         <v>0</v>
       </c>
       <c r="EP2" t="n">
-        <v>-0.04008472684269941</v>
+        <v>-0.003277067521953782</v>
       </c>
       <c r="EQ2" t="n">
         <v>-0</v>
@@ -1443,25 +1443,25 @@
         <v>-0</v>
       </c>
       <c r="ES2" t="n">
-        <v>-0.001669816990863851</v>
+        <v>-0.007404044403165143</v>
       </c>
       <c r="ET2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV2" t="n">
         <v>0</v>
       </c>
       <c r="EW2" t="n">
-        <v>0.009021039404655604</v>
+        <v>0.01858787383798866</v>
       </c>
       <c r="EX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY2" t="n">
-        <v>-0.02481397593768131</v>
+        <v>-0.03061436266506809</v>
       </c>
       <c r="EZ2" t="n">
         <v>-0</v>
@@ -1470,7 +1470,7 @@
         <v>-0</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.003701160958183631</v>
+        <v>-0.001170447452231095</v>
       </c>
       <c r="FC2" t="n">
         <v>-0</v>
@@ -1482,67 +1482,67 @@
         <v>0</v>
       </c>
       <c r="FF2" t="n">
-        <v>0.01880503875700162</v>
+        <v>0.01212769024603392</v>
       </c>
       <c r="FG2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH2" t="n">
-        <v>-0.03658236999083304</v>
+        <v>-0.01382468030277127</v>
       </c>
       <c r="FI2" t="n">
         <v>-0</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK2" t="n">
-        <v>-0.02100116366264682</v>
+        <v>-0.006098803169530619</v>
       </c>
       <c r="FL2" t="n">
         <v>0</v>
       </c>
       <c r="FM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO2" t="n">
-        <v>0.01347000657676283</v>
+        <v>0.05066637786979215</v>
       </c>
       <c r="FP2" t="n">
         <v>-0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>-0.05799466222915081</v>
+        <v>0.0173418304556385</v>
       </c>
       <c r="FR2" t="n">
         <v>-0</v>
       </c>
       <c r="FS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.01436510187931698</v>
+        <v>-0.02316612133399339</v>
       </c>
       <c r="FU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV2" t="n">
         <v>-0</v>
       </c>
       <c r="FW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX2" t="n">
-        <v>-0.0009095103352847149</v>
+        <v>0.001150034889505141</v>
       </c>
       <c r="FY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>-0.03261163536636261</v>
+        <v>-0.01028104848041611</v>
       </c>
       <c r="GA2" t="n">
         <v>0</v>
@@ -1554,16 +1554,16 @@
         <v>0</v>
       </c>
       <c r="GD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG2" t="n">
-        <v>0.03109619373412317</v>
+        <v>-0.006959121896406358</v>
       </c>
     </row>
     <row r="3">
@@ -2140,16 +2140,16 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.4925447775383084</v>
+        <v>0.1900048642496955</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2519668510534088</v>
+        <v>-0.151936273324198</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0517191162298009</v>
+        <v>-0.02304298579519583</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -2167,16 +2167,16 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.5875284781537423</v>
+        <v>0.3546051427335429</v>
       </c>
       <c r="L4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4151895019623455</v>
+        <v>-0.3833799787913703</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1913202039005849</v>
+        <v>-0.09421506101276071</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -2194,25 +2194,25 @@
         <v>-0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1623572509428594</v>
+        <v>0.0956412511548497</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1471857418536573</v>
+        <v>-0.06509101809913299</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.143626487556486</v>
+        <v>-0.09370880800169694</v>
       </c>
       <c r="X4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>-0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -2221,22 +2221,22 @@
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.2388952658085939</v>
+        <v>-0.01649082417897592</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0.04591922505456657</v>
+        <v>-0.115382619997827</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.007507051700719916</v>
+        <v>-0.04468969813494512</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>-0</v>
@@ -2248,22 +2248,22 @@
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.1076349480683945</v>
+        <v>0.1093557577161966</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN4" t="n">
-        <v>-0.08320255822474082</v>
+        <v>-0.09948624332676542</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.09718343074735972</v>
+        <v>0.08481741101681491</v>
       </c>
       <c r="AP4" t="n">
         <v>0</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR4" t="n">
         <v>-0</v>
@@ -2272,46 +2272,46 @@
         <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.107647766636082</v>
+        <v>0.4507002639830673</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW4" t="n">
-        <v>-0.119540186790753</v>
+        <v>-0.2574207924922184</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.1836566132853794</v>
+        <v>-0.2659023642274936</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC4" t="n">
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.08789992184236985</v>
+        <v>-0.05869858418996979</v>
       </c>
       <c r="BE4" t="n">
         <v>0</v>
       </c>
       <c r="BF4" t="n">
-        <v>-0.1028362036109141</v>
+        <v>0.006098002533967421</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.3073143410860486</v>
+        <v>-0.0800609719526011</v>
       </c>
       <c r="BH4" t="n">
         <v>0</v>
@@ -2320,7 +2320,7 @@
         <v>-0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK4" t="n">
         <v>0</v>
@@ -2329,22 +2329,22 @@
         <v>-0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.1814651202827573</v>
+        <v>-0.03522147339190375</v>
       </c>
       <c r="BN4" t="n">
         <v>-0</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.2021709770615403</v>
+        <v>0.01922480866632083</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.1291705966402735</v>
+        <v>-0.03826450326152566</v>
       </c>
       <c r="BQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
         <v>-0</v>
@@ -2356,19 +2356,19 @@
         <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.5525625600209984</v>
+        <v>0.3204012121513004</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX4" t="n">
-        <v>-0.0637332469978607</v>
+        <v>-0.1358629445563836</v>
       </c>
       <c r="BY4" t="n">
-        <v>-0.06051167682587903</v>
+        <v>-0.09063854202176096</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
         <v>-0</v>
@@ -2383,46 +2383,46 @@
         <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.2370635317737319</v>
+        <v>-0.1701629209815842</v>
       </c>
       <c r="CF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.05719688971151936</v>
+        <v>0.1799967634856074</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.05096282836557769</v>
+        <v>0.004692097039023127</v>
       </c>
       <c r="CI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK4" t="n">
         <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
         <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.005539889328328254</v>
+        <v>-0.02414903801549451</v>
       </c>
       <c r="CO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>-0.1292414680680091</v>
+        <v>0.1791931039576479</v>
       </c>
       <c r="CQ4" t="n">
-        <v>-0.02621069539297174</v>
+        <v>0.0451491442694333</v>
       </c>
       <c r="CR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS4" t="n">
         <v>-0</v>
@@ -2431,76 +2431,76 @@
         <v>-0</v>
       </c>
       <c r="CU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV4" t="n">
         <v>0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.1907922316072863</v>
+        <v>-0.159628641208567</v>
       </c>
       <c r="CX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.1251062558958605</v>
+        <v>0.1980534327343574</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.03822315800463594</v>
+        <v>0.009351563244502247</v>
       </c>
       <c r="DA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC4" t="n">
         <v>-0</v>
       </c>
       <c r="DD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE4" t="n">
         <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.01506810748933543</v>
+        <v>-0.03036376626323062</v>
       </c>
       <c r="DG4" t="n">
         <v>0</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.149960665041624</v>
+        <v>0.07293239602679334</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.09624134738984473</v>
+        <v>-0.07909521355820141</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM4" t="n">
         <v>0</v>
       </c>
       <c r="DN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.1032582164641537</v>
+        <v>-0.07851578322451806</v>
       </c>
       <c r="DP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.02120331022565368</v>
+        <v>0.1385658389275479</v>
       </c>
       <c r="DR4" t="n">
-        <v>-0.09166634307680743</v>
+        <v>-0.009763787668215453</v>
       </c>
       <c r="DS4" t="n">
         <v>0</v>
@@ -2518,25 +2518,25 @@
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>-0.04551095480626433</v>
+        <v>0.09102030024243825</v>
       </c>
       <c r="DY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>-0.02167512660600517</v>
+        <v>0.06579311166303463</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.08969622814239613</v>
+        <v>0.01233701217472441</v>
       </c>
       <c r="EB4" t="n">
         <v>0</v>
       </c>
       <c r="EC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE4" t="n">
         <v>-0</v>
@@ -2545,49 +2545,49 @@
         <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.1072746552948464</v>
+        <v>-0.0844298042995352</v>
       </c>
       <c r="EH4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.06523510574852824</v>
+        <v>0.1060211056813816</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.05998496320892268</v>
+        <v>0.04785436382577905</v>
       </c>
       <c r="EK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN4" t="n">
         <v>0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.1798273491514535</v>
+        <v>-0.07517166363125652</v>
       </c>
       <c r="EQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER4" t="n">
-        <v>-0.135063594374967</v>
+        <v>-0.1213785948840543</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0.1028709996348898</v>
+        <v>-0.05240932755108872</v>
       </c>
       <c r="ET4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV4" t="n">
         <v>0</v>
@@ -2599,46 +2599,46 @@
         <v>-0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.1828394369445057</v>
+        <v>-0.1751174351247088</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.104066184930018</v>
+        <v>0.2158652384210591</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.03949883083257574</v>
+        <v>-0.002645136567734776</v>
       </c>
       <c r="FC4" t="n">
         <v>-0</v>
       </c>
       <c r="FD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE4" t="n">
         <v>0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH4" t="n">
-        <v>-0.09408972847148034</v>
+        <v>-0.1091227894758848</v>
       </c>
       <c r="FI4" t="n">
         <v>-0</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.1354028911187474</v>
+        <v>0.123805447982157</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.002391365530326338</v>
+        <v>-0.01206436809178607</v>
       </c>
       <c r="FL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM4" t="n">
         <v>0</v>
@@ -2647,22 +2647,22 @@
         <v>-0</v>
       </c>
       <c r="FO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>-0.03544868794137361</v>
+        <v>0.05347754531532702</v>
       </c>
       <c r="FR4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS4" t="n">
-        <v>-0.04054397550309552</v>
+        <v>0.2445426152121762</v>
       </c>
       <c r="FT4" t="n">
-        <v>-0.1165088042768223</v>
+        <v>-0.05853019714945293</v>
       </c>
       <c r="FU4" t="n">
         <v>-0</v>
@@ -2674,19 +2674,19 @@
         <v>0</v>
       </c>
       <c r="FX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.04557198173757374</v>
+        <v>-0.09336914364401072</v>
       </c>
       <c r="GA4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB4" t="n">
-        <v>-0.02962589669049052</v>
+        <v>0.1257740942023932</v>
       </c>
       <c r="GC4" t="n">
         <v>0</v>
@@ -2698,10 +2698,10 @@
         <v>-0</v>
       </c>
       <c r="GF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -2709,52 +2709,52 @@
         <v>-0</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.4412128454942741</v>
+        <v>-0.08327902589679782</v>
       </c>
       <c r="C5" t="n">
         <v>-0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2380742141145797</v>
+        <v>0.06420409487434589</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001962670092837588</v>
+        <v>0.007516853012793616</v>
       </c>
       <c r="F5" t="n">
         <v>-0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03052890132386871</v>
+        <v>0.02269681106184641</v>
       </c>
       <c r="I5" t="n">
         <v>-0</v>
       </c>
       <c r="J5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.4535867542277735</v>
+        <v>-0.1388212696092534</v>
       </c>
       <c r="L5" t="n">
         <v>-0</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4877961673291774</v>
+        <v>0.1838280156623376</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1503164237160173</v>
+        <v>0.0667242318232622</v>
       </c>
       <c r="O5" t="n">
         <v>-0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.002513644987168867</v>
+        <v>0.0002572991213719065</v>
       </c>
       <c r="R5" t="n">
         <v>-0</v>
@@ -2763,43 +2763,43 @@
         <v>-0</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1527648503583922</v>
+        <v>-0.07337913052306798</v>
       </c>
       <c r="U5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>0.03866650543203792</v>
+        <v>0.05551747186707309</v>
       </c>
       <c r="W5" t="n">
-        <v>0.07002172654432867</v>
+        <v>0.1013640061372122</v>
       </c>
       <c r="X5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.005946327532580703</v>
+        <v>0.002938141435052093</v>
       </c>
       <c r="AA5" t="n">
         <v>-0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.2435313000797876</v>
+        <v>0.04359370591114528</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.0447633205961479</v>
+        <v>0.07221079186117904</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.001922609870031263</v>
+        <v>0.04686722220134051</v>
       </c>
       <c r="AG5" t="n">
         <v>-0</v>
@@ -2808,7 +2808,7 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.001413344692531528</v>
+        <v>-0.01779207831063017</v>
       </c>
       <c r="AJ5" t="n">
         <v>-0</v>
@@ -2817,70 +2817,70 @@
         <v>-0</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.1286121130972163</v>
+        <v>-0.05474277162426647</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.05327412938438266</v>
+        <v>0.0262083072592717</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.01659723752564988</v>
+        <v>-0.0621721519160112</v>
       </c>
       <c r="AP5" t="n">
         <v>-0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.04647515059166824</v>
+        <v>0.00423979184234178</v>
       </c>
       <c r="AS5" t="n">
         <v>-0</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.8680923608972122</v>
+        <v>-0.2809035489751275</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.2814870541885436</v>
+        <v>0.09272092424659727</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.09874423111925341</v>
+        <v>0.1896346135435477</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
         <v>-0</v>
       </c>
       <c r="BA5" t="n">
-        <v>0.07161887046855894</v>
+        <v>0.05182238362949373</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC5" t="n">
         <v>-0</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.1312919666629582</v>
+        <v>0.06581626448463879</v>
       </c>
       <c r="BE5" t="n">
         <v>-0</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.0638217826847207</v>
+        <v>0.0198201257450554</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.179634845074108</v>
+        <v>0.1149138497068549</v>
       </c>
       <c r="BH5" t="n">
         <v>-0</v>
@@ -2889,7 +2889,7 @@
         <v>0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.005723131456038344</v>
+        <v>0.006388279889372149</v>
       </c>
       <c r="BK5" t="n">
         <v>-0</v>
@@ -2898,52 +2898,52 @@
         <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.01142294999464607</v>
+        <v>0.03736060156335402</v>
       </c>
       <c r="BN5" t="n">
         <v>0</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.05298164611302532</v>
+        <v>0.01490455586177018</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.1274052990258057</v>
+        <v>0.04312472476317503</v>
       </c>
       <c r="BQ5" t="n">
         <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS5" t="n">
-        <v>0.03457379661758416</v>
+        <v>0.01401814447078668</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU5" t="n">
         <v>0</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.4501519402730482</v>
+        <v>-0.1602741577550862</v>
       </c>
       <c r="BW5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>0.09238222458733661</v>
+        <v>0.1293231094579794</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.02781625105653737</v>
+        <v>0.1318537927881213</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB5" t="n">
-        <v>0.06354108244406213</v>
+        <v>0.06202864417711452</v>
       </c>
       <c r="CC5" t="n">
         <v>-0</v>
@@ -2952,16 +2952,16 @@
         <v>0</v>
       </c>
       <c r="CE5" t="n">
-        <v>0.167199926602559</v>
+        <v>0.07273461351305119</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.0600046232286597</v>
+        <v>-0.05701184463793908</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.04079715136148356</v>
+        <v>-0.01150637778171289</v>
       </c>
       <c r="CI5" t="n">
         <v>0</v>
@@ -2970,7 +2970,7 @@
         <v>0</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.04177564542487567</v>
+        <v>0.02210775325973304</v>
       </c>
       <c r="CL5" t="n">
         <v>-0</v>
@@ -2979,43 +2979,43 @@
         <v>-0</v>
       </c>
       <c r="CN5" t="n">
-        <v>0.02667493930230281</v>
+        <v>0.02449715537040833</v>
       </c>
       <c r="CO5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CP5" t="n">
-        <v>0.04424876599818563</v>
+        <v>-0.06307743462072991</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.001969169395579331</v>
+        <v>-0.09336514027847805</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS5" t="n">
         <v>0</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0.05440610304482099</v>
+        <v>-0.01495287787420105</v>
       </c>
       <c r="CU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW5" t="n">
-        <v>0.1392500641099238</v>
+        <v>0.06879717244029381</v>
       </c>
       <c r="CX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY5" t="n">
-        <v>-0.104695228620408</v>
+        <v>-0.05891464141038689</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.03960744888208294</v>
+        <v>-0.01424500925385309</v>
       </c>
       <c r="DA5" t="n">
         <v>-0</v>
@@ -3024,7 +3024,7 @@
         <v>-0</v>
       </c>
       <c r="DC5" t="n">
-        <v>0.03564605069952453</v>
+        <v>0.008513465634998227</v>
       </c>
       <c r="DD5" t="n">
         <v>-0</v>
@@ -3033,52 +3033,52 @@
         <v>-0</v>
       </c>
       <c r="DF5" t="n">
-        <v>0.1938016577663339</v>
+        <v>0.04950948122343109</v>
       </c>
       <c r="DG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH5" t="n">
-        <v>-0.08517874668422319</v>
+        <v>-0.02927956055161714</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.02127589447954597</v>
+        <v>0.01519757940030952</v>
       </c>
       <c r="DJ5" t="n">
         <v>-0</v>
       </c>
       <c r="DK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL5" t="n">
-        <v>-0.003929146932315396</v>
+        <v>0.02546289780856886</v>
       </c>
       <c r="DM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO5" t="n">
-        <v>0.2105031661251997</v>
+        <v>-0.0134747722298563</v>
       </c>
       <c r="DP5" t="n">
         <v>0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0.03378768572313651</v>
+        <v>-0.1071049973754682</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.1414380797748401</v>
+        <v>0.0687098549877309</v>
       </c>
       <c r="DS5" t="n">
         <v>-0</v>
       </c>
       <c r="DT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU5" t="n">
-        <v>-0.03184116447395801</v>
+        <v>-0.02875665821976547</v>
       </c>
       <c r="DV5" t="n">
         <v>-0</v>
@@ -3087,16 +3087,16 @@
         <v>0</v>
       </c>
       <c r="DX5" t="n">
-        <v>0.01590987396387751</v>
+        <v>-0.0386255035687784</v>
       </c>
       <c r="DY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>0.08271414394139011</v>
+        <v>-0.04493280254439465</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.2093795113074675</v>
+        <v>0.08016336186391693</v>
       </c>
       <c r="EB5" t="n">
         <v>-0</v>
@@ -3105,79 +3105,79 @@
         <v>0</v>
       </c>
       <c r="ED5" t="n">
-        <v>0.04052936256748776</v>
+        <v>-0.05669970507789477</v>
       </c>
       <c r="EE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG5" t="n">
-        <v>0.05690018185269833</v>
+        <v>0.02217752646212477</v>
       </c>
       <c r="EH5" t="n">
         <v>0</v>
       </c>
       <c r="EI5" t="n">
-        <v>-0.1553954485572995</v>
+        <v>0.03974582974916913</v>
       </c>
       <c r="EJ5" t="n">
-        <v>-0.04512741228203281</v>
+        <v>-0.03475264791065123</v>
       </c>
       <c r="EK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL5" t="n">
         <v>0</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0.01302951619007284</v>
+        <v>0.03738248688634136</v>
       </c>
       <c r="EN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>0.07825627128956181</v>
+        <v>0.007440597431854499</v>
       </c>
       <c r="EQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER5" t="n">
-        <v>-0.1526278883178686</v>
+        <v>-0.004672866628516158</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.0344350956498696</v>
+        <v>0.0750126463525613</v>
       </c>
       <c r="ET5" t="n">
         <v>0</v>
       </c>
       <c r="EU5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV5" t="n">
-        <v>0.2051089294050598</v>
+        <v>-0.0237986410404609</v>
       </c>
       <c r="EW5" t="n">
         <v>0</v>
       </c>
       <c r="EX5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY5" t="n">
-        <v>0.1422293992060206</v>
+        <v>0.07783116555373287</v>
       </c>
       <c r="EZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA5" t="n">
-        <v>-0.08548114456900983</v>
+        <v>-0.09004379275713811</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.01116704594204621</v>
+        <v>-0.02313455431211497</v>
       </c>
       <c r="FC5" t="n">
         <v>0</v>
@@ -3186,52 +3186,52 @@
         <v>0</v>
       </c>
       <c r="FE5" t="n">
-        <v>0.03148469668135244</v>
+        <v>0.01482005755127496</v>
       </c>
       <c r="FF5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.08135978551047693</v>
+        <v>0.1142834042442211</v>
       </c>
       <c r="FI5" t="n">
         <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>0.03771012102898182</v>
+        <v>0.0676071056615799</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.07349715542384856</v>
+        <v>-0.03966097471558436</v>
       </c>
       <c r="FL5" t="n">
         <v>0</v>
       </c>
       <c r="FM5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN5" t="n">
-        <v>-0.001090717158994135</v>
+        <v>0.02583197637844808</v>
       </c>
       <c r="FO5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP5" t="n">
         <v>0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.0128375018688708</v>
+        <v>-0.1388334428340018</v>
       </c>
       <c r="FR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.02631804165113504</v>
+        <v>-0.1775768786082684</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.08110841527202993</v>
+        <v>0.1449489509503029</v>
       </c>
       <c r="FU5" t="n">
         <v>0</v>
@@ -3240,7 +3240,7 @@
         <v>0</v>
       </c>
       <c r="FW5" t="n">
-        <v>0.02646737034379698</v>
+        <v>-0.04592101269345232</v>
       </c>
       <c r="FX5" t="n">
         <v>-0</v>
@@ -3249,13 +3249,13 @@
         <v>-0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>0.1528054226978267</v>
+        <v>0.03992275618209092</v>
       </c>
       <c r="GA5" t="n">
         <v>-0</v>
       </c>
       <c r="GB5" t="n">
-        <v>0.07652098487617419</v>
+        <v>-0.03559395428981697</v>
       </c>
       <c r="GC5" t="n">
         <v>-0</v>
@@ -3267,7 +3267,7 @@
         <v>0</v>
       </c>
       <c r="GF5" t="n">
-        <v>-0.02168003854084612</v>
+        <v>0.02881208667531151</v>
       </c>
       <c r="GG5" t="n">
         <v>0</v>
@@ -3278,16 +3278,16 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.2912330186517463</v>
+        <v>0.2977355412363049</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1259429805697443</v>
+        <v>-0.1716596911880092</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.06348475179519404</v>
+        <v>0.04467776962185672</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -3299,22 +3299,22 @@
         <v>-0</v>
       </c>
       <c r="I6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4150257899853491</v>
+        <v>0.5424475529453695</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1947464640083141</v>
+        <v>-0.3975766147354446</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1197326412126568</v>
+        <v>0.03845750762029387</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -3329,73 +3329,73 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.121509154728858</v>
+        <v>0.156335555347572</v>
       </c>
       <c r="U6" t="n">
         <v>-0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.0419064330310817</v>
+        <v>-0.02044299955585291</v>
       </c>
       <c r="W6" t="n">
-        <v>0.05760785281818394</v>
+        <v>-0.09503791278445625</v>
       </c>
       <c r="X6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.03068737956371712</v>
+        <v>0.06287557468932571</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.02951313931872535</v>
+        <v>-0.2355247488049978</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.05551643453385607</v>
+        <v>0.006390291462142939</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.01531982356782924</v>
+        <v>0.1317488349727391</v>
       </c>
       <c r="AM6" t="n">
         <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.09899048015750149</v>
+        <v>-0.1332646419419702</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.07175607650624818</v>
+        <v>0.05912652058823156</v>
       </c>
       <c r="AP6" t="n">
         <v>0</v>
@@ -3410,46 +3410,46 @@
         <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.4284581433640243</v>
+        <v>0.5432507964866411</v>
       </c>
       <c r="AV6" t="n">
         <v>-0</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.1140759932264862</v>
+        <v>-0.2440120012287597</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.1581808154312296</v>
+        <v>-0.3056474710334741</v>
       </c>
       <c r="AY6" t="n">
         <v>-0</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC6" t="n">
         <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.04964646768505254</v>
+        <v>0.006218139634478737</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.07316985676790108</v>
+        <v>-0.1450481514090954</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.1290670750369897</v>
+        <v>0.07112290174020604</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
@@ -3458,7 +3458,7 @@
         <v>-0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK6" t="n">
         <v>0</v>
@@ -3467,16 +3467,16 @@
         <v>-0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.04708898810196428</v>
+        <v>0.01774455983202967</v>
       </c>
       <c r="BN6" t="n">
         <v>-0</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.08480782829282266</v>
+        <v>0.02848456969788835</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.1811237279643679</v>
+        <v>0.09924552495959475</v>
       </c>
       <c r="BQ6" t="n">
         <v>-0</v>
@@ -3494,73 +3494,73 @@
         <v>-0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.2279998885932671</v>
+        <v>0.4188978069023476</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0.02599512977998017</v>
+        <v>-0.1022404603987005</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.0949601851775484</v>
+        <v>0.0008999472075275351</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA6" t="n">
         <v>-0</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.1152515210628242</v>
+        <v>-0.1767302374306895</v>
       </c>
       <c r="CF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.04642539627083626</v>
+        <v>0.1932165694402461</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.008197476125266856</v>
+        <v>-0.06964234041522774</v>
       </c>
       <c r="CI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK6" t="n">
         <v>0</v>
       </c>
       <c r="CL6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM6" t="n">
         <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>-0.001947893108534842</v>
+        <v>-0.09291716953158391</v>
       </c>
       <c r="CO6" t="n">
         <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0.02957093309909326</v>
+        <v>0.1768827900882423</v>
       </c>
       <c r="CQ6" t="n">
-        <v>-0.08069532831037157</v>
+        <v>-0.01411048256546926</v>
       </c>
       <c r="CR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS6" t="n">
         <v>-0</v>
@@ -3569,103 +3569,103 @@
         <v>0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
         <v>-0</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.1145941227510069</v>
+        <v>-0.1597916613677358</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.07297549854201817</v>
+        <v>0.1906781788564723</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-0.003469055951012487</v>
+        <v>-0.06270383923837483</v>
       </c>
       <c r="DA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC6" t="n">
         <v>-0</v>
       </c>
       <c r="DD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.03802947460799849</v>
+        <v>-0.132842365545644</v>
       </c>
       <c r="DG6" t="n">
         <v>0</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.07445867450238723</v>
+        <v>0.08166113134993107</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.003305717621722952</v>
+        <v>-0.07327683605315044</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL6" t="n">
         <v>0</v>
       </c>
       <c r="DM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN6" t="n">
         <v>-0</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.00728526702782509</v>
+        <v>-0.1081985297259177</v>
       </c>
       <c r="DP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0.1217575864235073</v>
+        <v>-0.006035573344515626</v>
       </c>
       <c r="DR6" t="n">
-        <v>-0.07891627108589441</v>
+        <v>-0.05797424921686289</v>
       </c>
       <c r="DS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV6" t="n">
         <v>0</v>
       </c>
       <c r="DW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.09860804284149031</v>
+        <v>0.001529877686235067</v>
       </c>
       <c r="DY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>-0.04909257836396443</v>
+        <v>-0.1673773716842782</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.01139781810540425</v>
+        <v>-0.1736744256986235</v>
       </c>
       <c r="EB6" t="n">
         <v>0</v>
@@ -3674,34 +3674,34 @@
         <v>0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.1407197262203164</v>
+        <v>-0.1440662559746871</v>
       </c>
       <c r="EH6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.08304686552442951</v>
+        <v>0.1901539164484605</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.07793262601221548</v>
+        <v>-0.02706897362487894</v>
       </c>
       <c r="EK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL6" t="n">
         <v>-0</v>
       </c>
       <c r="EM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN6" t="n">
         <v>-0</v>
@@ -3710,136 +3710,136 @@
         <v>0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.08115806992203463</v>
+        <v>-0.1361788966576598</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.05571937757960718</v>
+        <v>0.07070617987447467</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.06118426929780665</v>
+        <v>0.0006061315988543681</v>
       </c>
       <c r="ET6" t="n">
         <v>-0</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV6" t="n">
         <v>0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.1123105817171017</v>
+        <v>-0.2158371345605143</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.05956199185454607</v>
+        <v>0.219342814638381</v>
       </c>
       <c r="FB6" t="n">
-        <v>-0.009940130339962456</v>
+        <v>-0.08411334525580576</v>
       </c>
       <c r="FC6" t="n">
         <v>-0</v>
       </c>
       <c r="FD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE6" t="n">
         <v>0</v>
       </c>
       <c r="FF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.001002499078042559</v>
+        <v>0.1175439977664934</v>
       </c>
       <c r="FI6" t="n">
         <v>-0</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.08555481866516007</v>
+        <v>0.142917041207651</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.03310872410491213</v>
+        <v>0.03132982825382059</v>
       </c>
       <c r="FL6" t="n">
         <v>-0</v>
       </c>
       <c r="FM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN6" t="n">
         <v>0</v>
       </c>
       <c r="FO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.04958691439521701</v>
+        <v>-0.091255472755759</v>
       </c>
       <c r="FR6" t="n">
         <v>-0</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.02745323040734057</v>
+        <v>0.05058354265130086</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.003686604811894609</v>
+        <v>0.1656002310859215</v>
       </c>
       <c r="FU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV6" t="n">
         <v>0</v>
       </c>
       <c r="FW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX6" t="n">
         <v>0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.002761705489629873</v>
+        <v>-0.1817038675459787</v>
       </c>
       <c r="GA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB6" t="n">
-        <v>-0.06357282629083627</v>
+        <v>0.1381318265701092</v>
       </c>
       <c r="GC6" t="n">
         <v>0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE6" t="n">
         <v>-0</v>
       </c>
       <c r="GF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -3847,46 +3847,46 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.2215294457763141</v>
+        <v>0.3766777487575211</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.07292556100962073</v>
+        <v>-0.1455406475900808</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.03840936272460374</v>
+        <v>-0.07082135499817933</v>
       </c>
       <c r="F7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
         <v>-0</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2952741051727642</v>
+        <v>0.7220460762943672</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.1389886555808135</v>
+        <v>-0.4694342106440199</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.07205261285037887</v>
+        <v>-0.2676418655702703</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P7" t="n">
         <v>-0</v>
@@ -3895,22 +3895,22 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.08319515716234173</v>
+        <v>0.1731822240260165</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.008112782759009875</v>
+        <v>-0.04486484917839326</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0862299729241931</v>
+        <v>-0.1915363423060021</v>
       </c>
       <c r="X7" t="n">
         <v>-0</v>
@@ -3919,82 +3919,82 @@
         <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.06290612005099692</v>
+        <v>0.1251445845521161</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.009947045032244318</v>
+        <v>-0.2581275197755136</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.003756650413871604</v>
+        <v>-0.09432652171914087</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.008022506820783861</v>
+        <v>0.1991798306593575</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0.07318639225217895</v>
+        <v>-0.05421424545163814</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.07819729714921661</v>
+        <v>-0.02126086039655552</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.3435160781296537</v>
+        <v>0.8208803136650785</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.05254825076382121</v>
+        <v>-0.2445320607192726</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.1244655343451792</v>
+        <v>-0.4727190951129448</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ7" t="n">
         <v>0</v>
@@ -4009,16 +4009,16 @@
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.02887613403341349</v>
+        <v>-0.04975413887107406</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
       </c>
       <c r="BF7" t="n">
-        <v>-0.04713903690923502</v>
+        <v>-0.09025744099818818</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.08400952520939282</v>
+        <v>0.05276701002644443</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
@@ -4027,28 +4027,28 @@
         <v>-0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
         <v>0</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.05747481498009885</v>
+        <v>0.1716161453810191</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.0607326632919934</v>
+        <v>0.03036252176287664</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.1944068900113273</v>
+        <v>0.1861326264491051</v>
       </c>
       <c r="BQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR7" t="n">
         <v>0</v>
@@ -4063,25 +4063,25 @@
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.1460796926760632</v>
+        <v>0.526898415022462</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.01094654792689349</v>
+        <v>-0.1351949816338177</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.07893386959125862</v>
+        <v>-0.1715909749825325</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
         <v>-0</v>
       </c>
       <c r="CB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC7" t="n">
         <v>-0</v>
@@ -4090,46 +4090,46 @@
         <v>0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.09029763527997021</v>
+        <v>-0.1929731790934917</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.02530133048427583</v>
+        <v>0.1696576509781248</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.009589838271585214</v>
+        <v>0.03244778264996265</v>
       </c>
       <c r="CI7" t="n">
         <v>0</v>
       </c>
       <c r="CJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK7" t="n">
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM7" t="n">
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.009219293617409521</v>
+        <v>-0.1650260538247008</v>
       </c>
       <c r="CO7" t="n">
         <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>-0.0448591618832721</v>
+        <v>0.1601465179245863</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.06084485668067902</v>
+        <v>0.01006617739189463</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
@@ -4138,55 +4138,55 @@
         <v>-0</v>
       </c>
       <c r="CU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.07883664192597548</v>
+        <v>-0.1777043156419784</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.04801208190669863</v>
+        <v>0.1942199653261692</v>
       </c>
       <c r="CZ7" t="n">
-        <v>-0.003055512558646003</v>
+        <v>0.01654336513280834</v>
       </c>
       <c r="DA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC7" t="n">
         <v>-0</v>
       </c>
       <c r="DD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE7" t="n">
         <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.03699421234084545</v>
+        <v>-0.06798548028793881</v>
       </c>
       <c r="DG7" t="n">
         <v>0</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.05527818634769013</v>
+        <v>0.1620820807924335</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.01630313676651526</v>
+        <v>-0.1728922514538394</v>
       </c>
       <c r="DJ7" t="n">
         <v>-0</v>
       </c>
       <c r="DK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL7" t="n">
         <v>0</v>
@@ -4195,28 +4195,28 @@
         <v>0</v>
       </c>
       <c r="DN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.004522031628229339</v>
+        <v>-0.1608505912419033</v>
       </c>
       <c r="DP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0.1391684627739203</v>
+        <v>-0.0588792093892614</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.03687881830634822</v>
+        <v>-0.0669544817659599</v>
       </c>
       <c r="DS7" t="n">
         <v>-0</v>
       </c>
       <c r="DT7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV7" t="n">
         <v>0</v>
@@ -4225,16 +4225,16 @@
         <v>0</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.07134862358237747</v>
+        <v>-0.02857810083991762</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>-0.002491310134305195</v>
+        <v>0.1331727871704446</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.02851595287307115</v>
+        <v>0.003241809707282485</v>
       </c>
       <c r="EB7" t="n">
         <v>0</v>
@@ -4243,25 +4243,25 @@
         <v>0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF7" t="n">
         <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.1375760180555673</v>
+        <v>-0.08510729414874832</v>
       </c>
       <c r="EH7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI7" t="n">
-        <v>-0.1025672845417293</v>
+        <v>-0.3219736723658741</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.08960254769907625</v>
+        <v>-0.04538584201998093</v>
       </c>
       <c r="EK7" t="n">
         <v>0</v>
@@ -4270,7 +4270,7 @@
         <v>-0</v>
       </c>
       <c r="EM7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN7" t="n">
         <v>-0</v>
@@ -4279,22 +4279,22 @@
         <v>0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.07518107642366693</v>
+        <v>-0.08273557411045065</v>
       </c>
       <c r="EQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.06084202097550825</v>
+        <v>0.0319818980141027</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.01767931064032646</v>
+        <v>0.01528195756393183</v>
       </c>
       <c r="ET7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
@@ -4306,49 +4306,49 @@
         <v>0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.08188566440611109</v>
+        <v>-0.2333989360125249</v>
       </c>
       <c r="EZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.02785583549192699</v>
+        <v>0.2039929521613185</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.008629177015525475</v>
+        <v>0.01595097315215781</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
       </c>
       <c r="FD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.04076639146552232</v>
+        <v>0.1225156999352775</v>
       </c>
       <c r="FI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.06015192160813492</v>
+        <v>0.09642333752413491</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.04747773589569526</v>
+        <v>-0.06495994686431629</v>
       </c>
       <c r="FL7" t="n">
         <v>-0</v>
       </c>
       <c r="FM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN7" t="n">
         <v>0</v>
@@ -4357,25 +4357,25 @@
         <v>0</v>
       </c>
       <c r="FP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.01082684880118945</v>
+        <v>-0.23187333705508</v>
       </c>
       <c r="FR7" t="n">
         <v>-0</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.07927208760040438</v>
+        <v>0.2458682708214253</v>
       </c>
       <c r="FT7" t="n">
-        <v>-0.02400735243379538</v>
+        <v>0.2591523194917482</v>
       </c>
       <c r="FU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW7" t="n">
         <v>0</v>
@@ -4384,57 +4384,57 @@
         <v>0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.03534584341666373</v>
+        <v>-0.1014279229750036</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
-        <v>-0.06942736944916554</v>
+        <v>0.05336706075922738</v>
       </c>
       <c r="GC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B8" t="n">
-        <v>-0.4128976292903803</v>
+        <v>-0.3552542819432422</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2347462186786795</v>
+        <v>0.2518679340999524</v>
       </c>
       <c r="D8" t="n">
         <v>-0</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1574777357017313</v>
+        <v>-0.0612597151322599</v>
       </c>
       <c r="F8" t="n">
         <v>-0</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1447695482584417</v>
+        <v>-0.03778610632222709</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I8" t="n">
         <v>-0</v>
@@ -4443,22 +4443,22 @@
         <v>-0</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5461972268402872</v>
+        <v>-0.685975730240566</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3181004715462106</v>
+        <v>0.4533610690738045</v>
       </c>
       <c r="M8" t="n">
         <v>-0</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2108840167708454</v>
+        <v>-0.06377311412130834</v>
       </c>
       <c r="O8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2296174628121881</v>
+        <v>-0.02095293446386069</v>
       </c>
       <c r="Q8" t="n">
         <v>-0</v>
@@ -4470,184 +4470,184 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.07089822675712093</v>
+        <v>-0.08579888135242947</v>
       </c>
       <c r="U8" t="n">
-        <v>0.04117169141305991</v>
+        <v>-0.1129412779471361</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.1296556931569572</v>
+        <v>-0.1435276411452542</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.04470744071871621</v>
+        <v>-0.02025612363317535</v>
       </c>
       <c r="Z8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.2423846936589006</v>
+        <v>-0.09219158566817348</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.001340973073021812</v>
+        <v>0.1587084411274342</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.04168582488341619</v>
+        <v>0.2260454701336529</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.1147558373131411</v>
+        <v>0.1640260224066217</v>
       </c>
       <c r="AI8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
         <v>-0</v>
       </c>
       <c r="AL8" t="n">
-        <v>-0.08380803552539445</v>
+        <v>-0.2397794805515459</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.1010104112569713</v>
+        <v>0.03668504323985311</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.1533017790398531</v>
+        <v>-0.2070274146265812</v>
       </c>
       <c r="AP8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.04275335659903277</v>
+        <v>0.04018280991403465</v>
       </c>
       <c r="AR8" t="n">
         <v>-0</v>
       </c>
       <c r="AS8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
         <v>-0</v>
       </c>
       <c r="AU8" t="n">
-        <v>-0.5266751986778992</v>
+        <v>-0.6726238385340226</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.2496263866185371</v>
+        <v>0.02160567166408806</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX8" t="n">
-        <v>-0.1263489086288088</v>
+        <v>-0.1935033036262581</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.3984603892701017</v>
+        <v>-0.05802298881922822</v>
       </c>
       <c r="BA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
         <v>-0</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD8" t="n">
-        <v>-0.2106867836117908</v>
+        <v>0.1721720657448023</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.1275526465709202</v>
+        <v>0.2576155548094021</v>
       </c>
       <c r="BF8" t="n">
         <v>-0</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.00753380437122339</v>
+        <v>0.1175969580879691</v>
       </c>
       <c r="BH8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.04560015982197758</v>
+        <v>0.02873719533754339</v>
       </c>
       <c r="BJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL8" t="n">
         <v>0</v>
       </c>
       <c r="BM8" t="n">
-        <v>-0.1429732460735647</v>
+        <v>0.09379389549129551</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.08742186173179757</v>
+        <v>-0.02020999880922615</v>
       </c>
       <c r="BO8" t="n">
         <v>0</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.06514196589273696</v>
+        <v>-0.02218078975719746</v>
       </c>
       <c r="BQ8" t="n">
         <v>0</v>
       </c>
       <c r="BR8" t="n">
-        <v>-0.01405421531790777</v>
+        <v>0.1378015062068807</v>
       </c>
       <c r="BS8" t="n">
         <v>0</v>
       </c>
       <c r="BT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU8" t="n">
         <v>0</v>
       </c>
       <c r="BV8" t="n">
-        <v>-0.1972521110101124</v>
+        <v>-0.3317014568154839</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.2939959978966352</v>
+        <v>0.01488313100603849</v>
       </c>
       <c r="BX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BY8" t="n">
-        <v>-0.01194427554679071</v>
+        <v>-0.1749733419110775</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.1025374228729074</v>
+        <v>-0.03566701064910531</v>
       </c>
       <c r="CB8" t="n">
         <v>0</v>
@@ -4656,28 +4656,28 @@
         <v>-0</v>
       </c>
       <c r="CD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.1620807446932567</v>
+        <v>0.2610441130328737</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.003903749908593334</v>
+        <v>-0.118321797200875</v>
       </c>
       <c r="CG8" t="n">
         <v>0</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.0468072489204082</v>
+        <v>0.02678645996246062</v>
       </c>
       <c r="CI8" t="n">
         <v>0</v>
       </c>
       <c r="CJ8" t="n">
-        <v>-0.1371438943520568</v>
+        <v>-0.03400479909149337</v>
       </c>
       <c r="CK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL8" t="n">
         <v>0</v>
@@ -4686,52 +4686,52 @@
         <v>-0</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.02520968671292398</v>
+        <v>0.1297726904953916</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.04827007999930594</v>
+        <v>-0.05049342424144766</v>
       </c>
       <c r="CP8" t="n">
         <v>0</v>
       </c>
       <c r="CQ8" t="n">
-        <v>-0.05054601072442669</v>
+        <v>-0.05906524010881115</v>
       </c>
       <c r="CR8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS8" t="n">
-        <v>-0.05232584504842004</v>
+        <v>-0.05275855856304928</v>
       </c>
       <c r="CT8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV8" t="n">
         <v>0</v>
       </c>
       <c r="CW8" t="n">
-        <v>0.1585718232992757</v>
+        <v>0.2675419676271525</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.02607409553105339</v>
+        <v>-0.1186373728135389</v>
       </c>
       <c r="CY8" t="n">
         <v>-0</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.08977675322816855</v>
+        <v>0.03206658793429923</v>
       </c>
       <c r="DA8" t="n">
         <v>-0</v>
       </c>
       <c r="DB8" t="n">
-        <v>-0.1158215670261881</v>
+        <v>-0.02653887495859777</v>
       </c>
       <c r="DC8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD8" t="n">
         <v>-0</v>
@@ -4740,49 +4740,49 @@
         <v>-0</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.1783960541369028</v>
+        <v>0.03918698483160317</v>
       </c>
       <c r="DG8" t="n">
-        <v>-0.02123166488886312</v>
+        <v>-0.1769800405299835</v>
       </c>
       <c r="DH8" t="n">
         <v>0</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.100577437078933</v>
+        <v>0.4500291292659264</v>
       </c>
       <c r="DJ8" t="n">
         <v>0</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.008857406421803809</v>
+        <v>0.02682631426149712</v>
       </c>
       <c r="DL8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN8" t="n">
         <v>-0</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.02895891218597415</v>
+        <v>0.08884376001020869</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.09197842967953181</v>
+        <v>-0.03904156240851576</v>
       </c>
       <c r="DQ8" t="n">
         <v>-0</v>
       </c>
       <c r="DR8" t="n">
-        <v>-0.03645843210126842</v>
+        <v>0.06139669542555819</v>
       </c>
       <c r="DS8" t="n">
         <v>0</v>
       </c>
       <c r="DT8" t="n">
-        <v>-0.03888697571651805</v>
+        <v>-0.1368188324755407</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
@@ -4794,79 +4794,79 @@
         <v>0</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.2641898210250115</v>
+        <v>0.1936335716700859</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.00988062661872606</v>
+        <v>0.03072447373798698</v>
       </c>
       <c r="DZ8" t="n">
         <v>0</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.06455277662303081</v>
+        <v>0.1183547124325032</v>
       </c>
       <c r="EB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.08431627934500005</v>
+        <v>0.18797037408226</v>
       </c>
       <c r="ED8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE8" t="n">
         <v>0</v>
       </c>
       <c r="EF8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.05324310162355382</v>
+        <v>0.1385309444223127</v>
       </c>
       <c r="EH8" t="n">
-        <v>-0.01783998674311225</v>
+        <v>0.02486803791030335</v>
       </c>
       <c r="EI8" t="n">
         <v>0</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.002375225129163624</v>
+        <v>-0.02606928082363725</v>
       </c>
       <c r="EK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL8" t="n">
-        <v>-0.1408266832990171</v>
+        <v>0.02852138187511449</v>
       </c>
       <c r="EM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP8" t="n">
-        <v>0.144843738040132</v>
+        <v>0.2051622960248339</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.07968517167084974</v>
+        <v>-0.05156743784638657</v>
       </c>
       <c r="ER8" t="n">
         <v>0</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.1563383894713316</v>
+        <v>-0.009873566284016064</v>
       </c>
       <c r="ET8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU8" t="n">
-        <v>-0.07110866300616059</v>
+        <v>0.03651076446188037</v>
       </c>
       <c r="EV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW8" t="n">
         <v>0</v>
@@ -4875,25 +4875,25 @@
         <v>-0</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.1498409865816004</v>
+        <v>0.3163083328616528</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0.004111229863635557</v>
+        <v>-0.1122703129256214</v>
       </c>
       <c r="FA8" t="n">
         <v>0</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.08339301578183805</v>
+        <v>0.01254420716583021</v>
       </c>
       <c r="FC8" t="n">
         <v>0</v>
       </c>
       <c r="FD8" t="n">
-        <v>-0.1319544819826578</v>
+        <v>-0.02964467154207953</v>
       </c>
       <c r="FE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF8" t="n">
         <v>0</v>
@@ -4902,99 +4902,99 @@
         <v>-0</v>
       </c>
       <c r="FH8" t="n">
-        <v>0.09451040359646638</v>
+        <v>-0.1168577639778944</v>
       </c>
       <c r="FI8" t="n">
-        <v>-0.01600931792502877</v>
+        <v>-0.188645708058295</v>
       </c>
       <c r="FJ8" t="n">
         <v>0</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.03748931125646107</v>
+        <v>-0.02982299591479754</v>
       </c>
       <c r="FL8" t="n">
         <v>-0</v>
       </c>
       <c r="FM8" t="n">
-        <v>0.01406186783559648</v>
+        <v>0.2169761236943102</v>
       </c>
       <c r="FN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>0.04998799891797678</v>
+        <v>0.1795416839002778</v>
       </c>
       <c r="FR8" t="n">
-        <v>-0.1246682376683335</v>
+        <v>0.09454290473828231</v>
       </c>
       <c r="FS8" t="n">
         <v>0</v>
       </c>
       <c r="FT8" t="n">
-        <v>0.06685152128631958</v>
+        <v>-0.06353847112317991</v>
       </c>
       <c r="FU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV8" t="n">
-        <v>-0.0002631093321151662</v>
+        <v>-0.01169032490663913</v>
       </c>
       <c r="FW8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY8" t="n">
         <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>-0.09763400758782255</v>
+        <v>0.2674604355772903</v>
       </c>
       <c r="GA8" t="n">
-        <v>0.08259453845194875</v>
+        <v>0.1230935807047338</v>
       </c>
       <c r="GB8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC8" t="n">
         <v>-0</v>
       </c>
       <c r="GD8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE8" t="n">
-        <v>0.07882311542406545</v>
+        <v>0.1567294883518115</v>
       </c>
       <c r="GF8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.2037616855707687</v>
+        <v>0.01938591712247523</v>
       </c>
       <c r="C9" t="n">
-        <v>-0.02111202638079063</v>
+        <v>-0.005815952733530489</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.07453040915224582</v>
+        <v>-0.006321023499902444</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -5009,22 +5009,22 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2124493438443137</v>
+        <v>0.02895757289845605</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.02298014275549642</v>
+        <v>-0.009516742471455491</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1358135947513372</v>
+        <v>-0.01177386171358227</v>
       </c>
       <c r="O9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
         <v>-0</v>
@@ -5039,25 +5039,25 @@
         <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.06370394910258421</v>
+        <v>0.007408857552449104</v>
       </c>
       <c r="U9" t="n">
-        <v>0.00715562447599368</v>
+        <v>0.0006443501512808594</v>
       </c>
       <c r="V9" t="n">
         <v>-0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.01093982352473709</v>
+        <v>0.008324744455993696</v>
       </c>
       <c r="X9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -5066,52 +5066,52 @@
         <v>-0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.06960918865395682</v>
+        <v>-0.002783366359043007</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.0004503920305753802</v>
+        <v>-0.009678727344399066</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.02386663544880818</v>
+        <v>-0.0091160803877988</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ9" t="n">
         <v>-0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.05400979619187804</v>
+        <v>0.01580983242141603</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.002885308591349655</v>
+        <v>-0.001696157839010942</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.001542373569656463</v>
+        <v>0.0149648727109168</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS9" t="n">
         <v>0</v>
@@ -5120,25 +5120,25 @@
         <v>-0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.2057405601822158</v>
+        <v>0.03212636278772488</v>
       </c>
       <c r="AV9" t="n">
-        <v>-0.001097531130955906</v>
+        <v>-0.002369608020230948</v>
       </c>
       <c r="AW9" t="n">
         <v>-0</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.001330109680954264</v>
+        <v>-0.00564118107528329</v>
       </c>
       <c r="AY9" t="n">
         <v>0</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BB9" t="n">
         <v>-0</v>
@@ -5147,19 +5147,19 @@
         <v>-0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.04405664842636203</v>
+        <v>-0.004300688302097478</v>
       </c>
       <c r="BE9" t="n">
-        <v>-0.02565169247062719</v>
+        <v>-0.004965681788897455</v>
       </c>
       <c r="BF9" t="n">
         <v>0</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.1011448406340567</v>
+        <v>-0.01256387757756859</v>
       </c>
       <c r="BH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI9" t="n">
         <v>-0</v>
@@ -5174,22 +5174,22 @@
         <v>-0</v>
       </c>
       <c r="BM9" t="n">
-        <v>-0.01488319929714037</v>
+        <v>0.0004647685475766495</v>
       </c>
       <c r="BN9" t="n">
-        <v>-0.003885603211754469</v>
+        <v>-0.002856063230777838</v>
       </c>
       <c r="BO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.02681290436986385</v>
+        <v>0.007223664720878127</v>
       </c>
       <c r="BQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS9" t="n">
         <v>-0</v>
@@ -5201,16 +5201,16 @@
         <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.1234095953553566</v>
+        <v>0.02711626252166407</v>
       </c>
       <c r="BW9" t="n">
-        <v>-0.05577912347590719</v>
+        <v>-0.003336243989503536</v>
       </c>
       <c r="BX9" t="n">
         <v>0</v>
       </c>
       <c r="BY9" t="n">
-        <v>-0.004856229366250841</v>
+        <v>0.008941348621753512</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -5225,19 +5225,19 @@
         <v>0</v>
       </c>
       <c r="CD9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.07122285520437725</v>
+        <v>-0.01047559447709829</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.0008877039067062208</v>
+        <v>0.00471218698986608</v>
       </c>
       <c r="CG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.01569000951385753</v>
+        <v>0.003734376489106014</v>
       </c>
       <c r="CI9" t="n">
         <v>0</v>
@@ -5255,19 +5255,19 @@
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.005064381418907848</v>
+        <v>-0.008023024274391017</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.004465978826537417</v>
+        <v>0.003170446984756561</v>
       </c>
       <c r="CP9" t="n">
         <v>-0</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.01578341147630363</v>
+        <v>0.00166315735079369</v>
       </c>
       <c r="CR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS9" t="n">
         <v>-0</v>
@@ -5279,19 +5279,19 @@
         <v>0</v>
       </c>
       <c r="CV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.06741073908357149</v>
+        <v>-0.008725587349965898</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0.01024663298676329</v>
+        <v>0.004184423034412578</v>
       </c>
       <c r="CY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.0006915745007767116</v>
+        <v>0.00195799261363263</v>
       </c>
       <c r="DA9" t="n">
         <v>0</v>
@@ -5309,16 +5309,16 @@
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.0946185707682474</v>
+        <v>-0.002474414104898611</v>
       </c>
       <c r="DG9" t="n">
-        <v>-0.003410635528069239</v>
+        <v>0.002634869489367975</v>
       </c>
       <c r="DH9" t="n">
         <v>0</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.02254218818363217</v>
+        <v>-0.0008767279636834656</v>
       </c>
       <c r="DJ9" t="n">
         <v>-0</v>
@@ -5333,22 +5333,22 @@
         <v>-0</v>
       </c>
       <c r="DN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.03691057466195077</v>
+        <v>-0.006107946822850827</v>
       </c>
       <c r="DP9" t="n">
-        <v>-0.01160526093311547</v>
+        <v>-0.002824287589067227</v>
       </c>
       <c r="DQ9" t="n">
         <v>0</v>
       </c>
       <c r="DR9" t="n">
-        <v>-0.02722752154917827</v>
+        <v>0.007151599610833796</v>
       </c>
       <c r="DS9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT9" t="n">
         <v>-0</v>
@@ -5357,25 +5357,25 @@
         <v>-0</v>
       </c>
       <c r="DV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.05427311811087433</v>
+        <v>0.008244284861400716</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.004578340224248666</v>
+        <v>0.004032484085526445</v>
       </c>
       <c r="DZ9" t="n">
         <v>-0</v>
       </c>
       <c r="EA9" t="n">
-        <v>-0.02546200788514089</v>
+        <v>-0.0075465614325482</v>
       </c>
       <c r="EB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC9" t="n">
         <v>0</v>
@@ -5387,19 +5387,19 @@
         <v>-0</v>
       </c>
       <c r="EF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.0386073250226083</v>
+        <v>-0.002453062793012623</v>
       </c>
       <c r="EH9" t="n">
-        <v>-0.005391510005268511</v>
+        <v>-0.0002344342530739109</v>
       </c>
       <c r="EI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.03249880296707638</v>
+        <v>0.0005250211621889365</v>
       </c>
       <c r="EK9" t="n">
         <v>0</v>
@@ -5411,28 +5411,28 @@
         <v>-0</v>
       </c>
       <c r="EN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO9" t="n">
         <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.04355050220434932</v>
+        <v>-0.009656725128069043</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.02539467715313222</v>
+        <v>-0.002119707093852378</v>
       </c>
       <c r="ER9" t="n">
         <v>-0</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.03438668183436552</v>
+        <v>-0.002096908900793363</v>
       </c>
       <c r="ET9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
         <v>-0</v>
@@ -5441,19 +5441,19 @@
         <v>-0</v>
       </c>
       <c r="EX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.07053976692866877</v>
+        <v>-0.01060308952195746</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0.001652809153096199</v>
+        <v>0.004253046531855556</v>
       </c>
       <c r="FA9" t="n">
         <v>-0</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.009248683371999614</v>
+        <v>0.0009868910431247992</v>
       </c>
       <c r="FC9" t="n">
         <v>-0</v>
@@ -5471,52 +5471,52 @@
         <v>-0</v>
       </c>
       <c r="FH9" t="n">
-        <v>-0.02176838330341586</v>
+        <v>-0.0008003625051733404</v>
       </c>
       <c r="FI9" t="n">
-        <v>-0.0001830194439178256</v>
+        <v>0.008822503809556737</v>
       </c>
       <c r="FJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FK9" t="n">
-        <v>-0.04577881333404821</v>
+        <v>-0.0084338401739212</v>
       </c>
       <c r="FL9" t="n">
         <v>-0</v>
       </c>
       <c r="FM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>-0.02634833274302657</v>
+        <v>-0.01556038327128378</v>
       </c>
       <c r="FR9" t="n">
-        <v>0.0148731690951812</v>
+        <v>0.004669411841273141</v>
       </c>
       <c r="FS9" t="n">
         <v>-0</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.04452370605113253</v>
+        <v>0.007744555751278089</v>
       </c>
       <c r="FU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX9" t="n">
         <v>0</v>
@@ -5525,10 +5525,10 @@
         <v>-0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-0.00657073855393182</v>
+        <v>-0.007728857027640932</v>
       </c>
       <c r="GA9" t="n">
-        <v>0.01205343400981358</v>
+        <v>-0.00564021587999568</v>
       </c>
       <c r="GB9" t="n">
         <v>-0</v>
@@ -5537,16 +5537,16 @@
         <v>0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE9" t="n">
         <v>-0</v>
       </c>
       <c r="GF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="10">
@@ -5554,7 +5554,7 @@
         <v>-0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7316497964849361</v>
+        <v>0.09757761094983913</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -5563,25 +5563,25 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1504203808717845</v>
+        <v>-0.009824665861901082</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2478125178456526</v>
+        <v>-0.01450368606525083</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8208933052107177</v>
+        <v>0.1656726148294078</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -5590,25 +5590,25 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2311488351659118</v>
+        <v>-0.04054185586052782</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.3479260319567859</v>
+        <v>-0.006038928862851419</v>
       </c>
       <c r="S10" t="n">
         <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.2141729787127018</v>
+        <v>0.02345635505928542</v>
       </c>
       <c r="U10" t="n">
         <v>-0</v>
@@ -5617,88 +5617,88 @@
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.07214389403961539</v>
+        <v>-0.01988576789059593</v>
       </c>
       <c r="X10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z10" t="n">
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0.1167806264512214</v>
+        <v>0.001411900979224597</v>
       </c>
       <c r="AB10" t="n">
         <v>-0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.2078110202534718</v>
+        <v>-0.03796573098387846</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.07359300640673076</v>
+        <v>-0.03244484805817233</v>
       </c>
       <c r="AG10" t="n">
         <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0.0335587736411025</v>
+        <v>0.0201189227465572</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.150986600878547</v>
+        <v>0.03383491830679402</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN10" t="n">
         <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.06514462883925401</v>
+        <v>0.01488923527609277</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR10" t="n">
         <v>-0</v>
       </c>
       <c r="AS10" t="n">
-        <v>-0.07262809757700661</v>
+        <v>-0.01511916011531341</v>
       </c>
       <c r="AT10" t="n">
         <v>-0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.7537182816382747</v>
+        <v>0.1663464421931702</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
       </c>
       <c r="AW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.105320110723552</v>
+        <v>-0.02681604223203846</v>
       </c>
       <c r="AY10" t="n">
         <v>0</v>
@@ -5707,16 +5707,16 @@
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB10" t="n">
-        <v>-0.1720635169744985</v>
+        <v>0.004751906177449138</v>
       </c>
       <c r="BC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.188747437584719</v>
+        <v>-0.007198749914782061</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
@@ -5725,79 +5725,79 @@
         <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.3107332143131121</v>
+        <v>-0.02721994392205762</v>
       </c>
       <c r="BH10" t="n">
         <v>0</v>
       </c>
       <c r="BI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK10" t="n">
-        <v>-0.1549181673341322</v>
+        <v>-0.02098837875274131</v>
       </c>
       <c r="BL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>-0.01471019285214604</v>
+        <v>0.002636661309614037</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
       </c>
       <c r="BO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.2303369133668126</v>
+        <v>0.03933040195717115</v>
       </c>
       <c r="BQ10" t="n">
         <v>-0</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
         <v>-0</v>
       </c>
       <c r="BT10" t="n">
-        <v>0.06669957886274705</v>
+        <v>0.02620365175056464</v>
       </c>
       <c r="BU10" t="n">
         <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.4579459178585492</v>
+        <v>0.1101942131791429</v>
       </c>
       <c r="BW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.09146754569169431</v>
+        <v>-0.01479872811889521</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB10" t="n">
         <v>0</v>
       </c>
       <c r="CC10" t="n">
-        <v>-0.1145634698028519</v>
+        <v>-0.009961327371820832</v>
       </c>
       <c r="CD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.2200620739475095</v>
+        <v>-0.04447183478732588</v>
       </c>
       <c r="CF10" t="n">
         <v>-0</v>
@@ -5806,37 +5806,37 @@
         <v>-0</v>
       </c>
       <c r="CH10" t="n">
-        <v>-2.84623692878538e-05</v>
+        <v>0.01212113248288962</v>
       </c>
       <c r="CI10" t="n">
         <v>-0</v>
       </c>
       <c r="CJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.1198573095767745</v>
+        <v>0.009752809541005032</v>
       </c>
       <c r="CM10" t="n">
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.04019479521914748</v>
+        <v>-0.03633331107018484</v>
       </c>
       <c r="CO10" t="n">
         <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.09851059397922572</v>
+        <v>0.01631205761356714</v>
       </c>
       <c r="CR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS10" t="n">
         <v>-0</v>
@@ -5845,22 +5845,22 @@
         <v>-0</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.004513521845497038</v>
+        <v>0.006560787932244765</v>
       </c>
       <c r="CV10" t="n">
         <v>-0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.2106254066567632</v>
+        <v>-0.04622986886535319</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
         <v>0</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-0.01319814886706306</v>
+        <v>0.004523044830878994</v>
       </c>
       <c r="DA10" t="n">
         <v>0</v>
@@ -5872,25 +5872,25 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.1084204634958661</v>
+        <v>0.01023894258392583</v>
       </c>
       <c r="DE10" t="n">
         <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.3860335444746215</v>
+        <v>-0.03204091402384493</v>
       </c>
       <c r="DG10" t="n">
         <v>-0</v>
       </c>
       <c r="DH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.06215665004210663</v>
+        <v>-0.008533743261384931</v>
       </c>
       <c r="DJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK10" t="n">
         <v>0</v>
@@ -5899,40 +5899,40 @@
         <v>-0</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.04632315912626006</v>
+        <v>-0.0003088875521364118</v>
       </c>
       <c r="DN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.07817088537638797</v>
+        <v>-0.01944579776823729</v>
       </c>
       <c r="DP10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR10" t="n">
-        <v>-0.02523504565473022</v>
+        <v>0.03309878732703857</v>
       </c>
       <c r="DS10" t="n">
         <v>-0</v>
       </c>
       <c r="DT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>-0.007381071188496106</v>
+        <v>0.0176963690190048</v>
       </c>
       <c r="DW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>0.1399852493032584</v>
+        <v>0.01368524716570474</v>
       </c>
       <c r="DY10" t="n">
         <v>-0</v>
@@ -5941,10 +5941,10 @@
         <v>-0</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.05888798190790111</v>
+        <v>-0.001206912833149594</v>
       </c>
       <c r="EB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC10" t="n">
         <v>-0</v>
@@ -5953,25 +5953,25 @@
         <v>-0</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.04767795582855436</v>
+        <v>-0.01045384833754833</v>
       </c>
       <c r="EF10" t="n">
         <v>0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.1342468974963269</v>
+        <v>-0.02253563088881311</v>
       </c>
       <c r="EH10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.03119636325961404</v>
+        <v>-0.01537328313917171</v>
       </c>
       <c r="EK10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL10" t="n">
         <v>-0</v>
@@ -5980,40 +5980,40 @@
         <v>-0</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.163991562593833</v>
+        <v>0.002847922990024203</v>
       </c>
       <c r="EO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.144718052127662</v>
+        <v>-0.03016084617831736</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER10" t="n">
         <v>-0</v>
       </c>
       <c r="ES10" t="n">
-        <v>-0.03491837295012512</v>
+        <v>-0.00547044442179326</v>
       </c>
       <c r="ET10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV10" t="n">
         <v>-0</v>
       </c>
       <c r="EW10" t="n">
-        <v>0.03666684645873523</v>
+        <v>0.01695121094726356</v>
       </c>
       <c r="EX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.2320760197343417</v>
+        <v>-0.04761050431764294</v>
       </c>
       <c r="EZ10" t="n">
         <v>-0</v>
@@ -6022,52 +6022,52 @@
         <v>-0</v>
       </c>
       <c r="FB10" t="n">
-        <v>-0.02924192806036417</v>
+        <v>0.0003099238861585297</v>
       </c>
       <c r="FC10" t="n">
         <v>-0</v>
       </c>
       <c r="FD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
         <v>-0</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.07630994049075909</v>
+        <v>0.008213863441663834</v>
       </c>
       <c r="FG10" t="n">
         <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>-0.128414093765179</v>
+        <v>-0.03920370870441226</v>
       </c>
       <c r="FI10" t="n">
         <v>0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.1122339145420345</v>
+        <v>-0.0009522527515419129</v>
       </c>
       <c r="FL10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN10" t="n">
         <v>0</v>
       </c>
       <c r="FO10" t="n">
-        <v>0.01936776781749308</v>
+        <v>0.03415061105190867</v>
       </c>
       <c r="FP10" t="n">
         <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.1393094105116507</v>
+        <v>-0.08769355274952161</v>
       </c>
       <c r="FR10" t="n">
         <v>-0</v>
@@ -6076,7 +6076,7 @@
         <v>-0</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.07219713600154107</v>
+        <v>-0.01421421016979062</v>
       </c>
       <c r="FU10" t="n">
         <v>-0</v>
@@ -6088,13 +6088,13 @@
         <v>-0</v>
       </c>
       <c r="FX10" t="n">
-        <v>-0.02283278273335787</v>
+        <v>-0.005107639540496368</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.1229902096805769</v>
+        <v>-0.03273527251524428</v>
       </c>
       <c r="GA10" t="n">
         <v>0</v>
@@ -6106,16 +6106,16 @@
         <v>0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.03652050614757956</v>
+        <v>-0.0172088087846109</v>
       </c>
     </row>
     <row r="11">
@@ -6692,22 +6692,22 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.4364127009986698</v>
+        <v>0.6229069891064934</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.1222600383834697</v>
+        <v>-0.2304886913832773</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.08417654500053544</v>
+        <v>0.05389890825083962</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H12" t="n">
         <v>-0</v>
@@ -6719,22 +6719,22 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.4325768781182674</v>
+        <v>0.76016183565662</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1651008900520076</v>
+        <v>-0.401147517369201</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1390727065953216</v>
+        <v>-0.05670337860192001</v>
       </c>
       <c r="O12" t="n">
         <v>-0</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -6743,73 +6743,73 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.1574510280963652</v>
+        <v>0.1877695501895166</v>
       </c>
       <c r="U12" t="n">
         <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>0.02691585709812528</v>
+        <v>-0.09120220074408446</v>
       </c>
       <c r="W12" t="n">
-        <v>0.03521905659133234</v>
+        <v>-0.1412552413462852</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.1048627604438015</v>
+        <v>-0.1280594842970837</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0.02477445796860505</v>
+        <v>-0.2849924237822738</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.0266085246064047</v>
+        <v>-0.09326628726564136</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.07105075723151431</v>
+        <v>0.2222315190977919</v>
       </c>
       <c r="AM12" t="n">
         <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.05206607875585138</v>
+        <v>-0.1085995977872902</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.03925925811019379</v>
+        <v>0.1739503529415117</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
@@ -6824,55 +6824,55 @@
         <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.4565639240459538</v>
+        <v>0.5862950665562959</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.01483221644763541</v>
+        <v>-0.195753071245347</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.14259154724045</v>
+        <v>-0.3456058233333751</v>
       </c>
       <c r="AY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ12" t="n">
         <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.02802216407627916</v>
+        <v>0.0892098685034375</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0.0767627917934577</v>
+        <v>-0.02675939770961097</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.2210005319640361</v>
+        <v>0.05190717358735815</v>
       </c>
       <c r="BH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
@@ -6881,19 +6881,19 @@
         <v>-0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.03697696096497962</v>
+        <v>-0.05751882551497325</v>
       </c>
       <c r="BN12" t="n">
         <v>-0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.02412516321265624</v>
+        <v>-0.06769168378369678</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.0957952109796202</v>
+        <v>0.06563979802668818</v>
       </c>
       <c r="BQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR12" t="n">
         <v>0</v>
@@ -6908,43 +6908,43 @@
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.262977387409031</v>
+        <v>0.5415538224761839</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>0.007014187649297195</v>
+        <v>-0.2317898290575354</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.0729577588668268</v>
+        <v>-0.05834386744495751</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB12" t="n">
         <v>0</v>
       </c>
       <c r="CC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.1204097784851455</v>
+        <v>-0.2143393008471898</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.01115003453073963</v>
+        <v>0.1865508745315096</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.01647929252555992</v>
+        <v>-0.03776949184704866</v>
       </c>
       <c r="CI12" t="n">
         <v>0</v>
@@ -6962,19 +6962,19 @@
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.01075848988723854</v>
+        <v>-0.1241087920752982</v>
       </c>
       <c r="CO12" t="n">
         <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.05138775577135381</v>
+        <v>0.2148439690929947</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.0846237364191272</v>
+        <v>0.01805305815089667</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
         <v>-0</v>
@@ -6983,28 +6983,28 @@
         <v>-0</v>
       </c>
       <c r="CU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.1101978538685355</v>
+        <v>-0.1959219915676942</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.02795376246541411</v>
+        <v>0.1839479678534581</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.02432707620095008</v>
+        <v>-0.02760201099442325</v>
       </c>
       <c r="DA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC12" t="n">
         <v>-0</v>
@@ -7016,46 +7016,46 @@
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.1369275889431344</v>
+        <v>-0.2881727654336388</v>
       </c>
       <c r="DG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.02705193792472179</v>
+        <v>0.01416984054523919</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.03899167868768724</v>
+        <v>-0.1097888867877578</v>
       </c>
       <c r="DJ12" t="n">
         <v>-0</v>
       </c>
       <c r="DK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL12" t="n">
         <v>0</v>
       </c>
       <c r="DM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.04102429553835134</v>
+        <v>-0.1152625896426797</v>
       </c>
       <c r="DP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>-0.0921577845030614</v>
+        <v>0.1596627945339916</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.05045974928374376</v>
+        <v>0.05954446981563372</v>
       </c>
       <c r="DS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT12" t="n">
         <v>-0</v>
@@ -7067,25 +7067,25 @@
         <v>0</v>
       </c>
       <c r="DW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.06489857043054807</v>
+        <v>0.01696740015864889</v>
       </c>
       <c r="DY12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>-0.03431605098793519</v>
+        <v>-0.04010568933755559</v>
       </c>
       <c r="EA12" t="n">
-        <v>-0.04124955170766773</v>
+        <v>0.03468349319717069</v>
       </c>
       <c r="EB12" t="n">
         <v>0</v>
       </c>
       <c r="EC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED12" t="n">
         <v>0</v>
@@ -7094,52 +7094,52 @@
         <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.08522782202366673</v>
+        <v>-0.1871211580789953</v>
       </c>
       <c r="EH12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.03961721085029832</v>
+        <v>0.1205949645340095</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.05732087660831015</v>
+        <v>-0.01664072866861653</v>
       </c>
       <c r="EK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL12" t="n">
         <v>-0</v>
       </c>
       <c r="EM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN12" t="n">
         <v>-0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.09141417003815153</v>
+        <v>-0.09006945341964696</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.03922352804181977</v>
+        <v>0.03697312378076693</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.02388402373576547</v>
+        <v>-0.1358474950923219</v>
       </c>
       <c r="ET12" t="n">
         <v>-0</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV12" t="n">
         <v>0</v>
@@ -7148,25 +7148,25 @@
         <v>-0</v>
       </c>
       <c r="EX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.111021318247276</v>
+        <v>-0.2279298519373604</v>
       </c>
       <c r="EZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.02791561438486882</v>
+        <v>0.2072510289734306</v>
       </c>
       <c r="FB12" t="n">
-        <v>-0.02114534413813288</v>
+        <v>-0.05343248167643232</v>
       </c>
       <c r="FC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE12" t="n">
         <v>0</v>
@@ -7175,19 +7175,19 @@
         <v>-0</v>
       </c>
       <c r="FG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.02413317163026585</v>
+        <v>-0.1875899724285907</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.06713840594655165</v>
+        <v>0.1402634813326789</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.0808984636754793</v>
+        <v>-0.01808192701838869</v>
       </c>
       <c r="FL12" t="n">
         <v>-0</v>
@@ -7196,49 +7196,49 @@
         <v>0</v>
       </c>
       <c r="FN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.06168525562620482</v>
+        <v>-0.3352956319661995</v>
       </c>
       <c r="FR12" t="n">
         <v>-0</v>
       </c>
       <c r="FS12" t="n">
-        <v>0.1381350728665878</v>
+        <v>0.3400231466097192</v>
       </c>
       <c r="FT12" t="n">
-        <v>-0.0582806894589532</v>
+        <v>0.1917464180749557</v>
       </c>
       <c r="FU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX12" t="n">
         <v>0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.004918809312884615</v>
+        <v>-0.286429285452208</v>
       </c>
       <c r="GA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0.0555991045602135</v>
+        <v>0.1905125569551358</v>
       </c>
       <c r="GC12" t="n">
         <v>0</v>
@@ -7250,10 +7250,10 @@
         <v>-0</v>
       </c>
       <c r="GF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -7261,7 +7261,7 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.7896572283882904</v>
+        <v>0.5934808219112925</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -7270,13 +7270,13 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.09724943569593857</v>
+        <v>-0.001391162601149037</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4801103547756475</v>
+        <v>-0.351341102381747</v>
       </c>
       <c r="G13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>-0</v>
@@ -7288,7 +7288,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7862291278148225</v>
+        <v>0.989222312454159</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -7297,16 +7297,16 @@
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.03762006579171671</v>
+        <v>-0.3186001248841479</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.8108024257131298</v>
+        <v>-0.5386551199464851</v>
       </c>
       <c r="P13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -7315,7 +7315,7 @@
         <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1132842841366111</v>
+        <v>0.1388543912970074</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -7324,25 +7324,25 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.165736665959958</v>
+        <v>-0.1235877993452758</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.04497996912847784</v>
+        <v>-0.1534068127939599</v>
       </c>
       <c r="Y13" t="n">
         <v>-0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB13" t="n">
         <v>-0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.04006121745721534</v>
+        <v>0.05950294573750579</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -7351,10 +7351,10 @@
         <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.03730960109521671</v>
+        <v>-0.335596285043086</v>
       </c>
       <c r="AG13" t="n">
-        <v>0.02523393848985387</v>
+        <v>-0.01248862390082369</v>
       </c>
       <c r="AH13" t="n">
         <v>-0</v>
@@ -7363,13 +7363,13 @@
         <v>-0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.1691114258848674</v>
+        <v>0.09496026016714625</v>
       </c>
       <c r="AM13" t="n">
         <v>0</v>
@@ -7378,13 +7378,13 @@
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.07400135615353011</v>
+        <v>-0.03494656333792734</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.1908076001708986</v>
+        <v>-0.1255220061323424</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR13" t="n">
         <v>-0</v>
@@ -7393,10 +7393,10 @@
         <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.6791535627584835</v>
+        <v>0.9912649017464488</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
@@ -7405,13 +7405,13 @@
         <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>-0.06784846483430823</v>
+        <v>-0.266066041340225</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0.5545105244430468</v>
+        <v>-0.449496721476578</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA13" t="n">
         <v>-0</v>
@@ -7420,10 +7420,10 @@
         <v>0</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.2135758827565682</v>
+        <v>-0.1094025284671624</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
@@ -7432,40 +7432,40 @@
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.17639221010928</v>
+        <v>0.07421706987819841</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0.1740219637820641</v>
+        <v>-0.03839815958889962</v>
       </c>
       <c r="BI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.1793128249174742</v>
+        <v>0.2118658641040944</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO13" t="n">
         <v>-0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.004965480991825745</v>
+        <v>0.1451423970323311</v>
       </c>
       <c r="BQ13" t="n">
-        <v>-8.207899720864709e-05</v>
+        <v>0.07273328266258706</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
         <v>-0</v>
@@ -7477,7 +7477,7 @@
         <v>-0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.3898603636480943</v>
+        <v>0.5860080265032681</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
@@ -7486,10 +7486,10 @@
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>-0.1089402438495041</v>
+        <v>-0.1283535458184499</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0.2970971847311159</v>
+        <v>-0.2861579141631228</v>
       </c>
       <c r="CA13" t="n">
         <v>-0</v>
@@ -7504,7 +7504,7 @@
         <v>-0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.1677940148055812</v>
+        <v>-0.2547717058890044</v>
       </c>
       <c r="CF13" t="n">
         <v>0</v>
@@ -7513,13 +7513,13 @@
         <v>-0</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.03398383854159838</v>
+        <v>0.05161582395578654</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.142046889693274</v>
+        <v>0.1758753890825504</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
         <v>0</v>
@@ -7531,22 +7531,22 @@
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.004100011823788998</v>
+        <v>-0.2511542316397242</v>
       </c>
       <c r="CO13" t="n">
         <v>-0</v>
       </c>
       <c r="CP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>0.001550350905557011</v>
+        <v>0.04186937403523842</v>
       </c>
       <c r="CR13" t="n">
-        <v>0.02723126931539167</v>
+        <v>0.06042007703025925</v>
       </c>
       <c r="CS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT13" t="n">
         <v>-0</v>
@@ -7555,49 +7555,49 @@
         <v>-0</v>
       </c>
       <c r="CV13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.1406216491391074</v>
+        <v>-0.2556871709370001</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
         <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.04688324013634841</v>
+        <v>0.01676940258872459</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.1746702004523784</v>
+        <v>0.1883372724803561</v>
       </c>
       <c r="DB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE13" t="n">
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.08331876198993519</v>
+        <v>-0.06810571733113911</v>
       </c>
       <c r="DG13" t="n">
         <v>0</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.1131738862569511</v>
+        <v>-0.2279560178926304</v>
       </c>
       <c r="DJ13" t="n">
-        <v>-0.05552828535873072</v>
+        <v>0.07469678539065266</v>
       </c>
       <c r="DK13" t="n">
         <v>0</v>
@@ -7606,55 +7606,55 @@
         <v>0</v>
       </c>
       <c r="DM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.004670346733203089</v>
+        <v>-0.1259515172759061</v>
       </c>
       <c r="DP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>-0.02388871749658413</v>
+        <v>0.07908138994962505</v>
       </c>
       <c r="DS13" t="n">
-        <v>-2.358016954926391e-05</v>
+        <v>0.1255713539506271</v>
       </c>
       <c r="DT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU13" t="n">
         <v>-0</v>
       </c>
       <c r="DV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW13" t="n">
         <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>-0.1186267048178468</v>
+        <v>-0.1766089894121963</v>
       </c>
       <c r="DY13" t="n">
         <v>0</v>
       </c>
       <c r="DZ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.01355393993915582</v>
+        <v>-0.01946241899304349</v>
       </c>
       <c r="EB13" t="n">
-        <v>-0.07281284466190099</v>
+        <v>-0.1123662630803027</v>
       </c>
       <c r="EC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED13" t="n">
         <v>0</v>
@@ -7663,64 +7663,64 @@
         <v>-0</v>
       </c>
       <c r="EF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.1596292374703757</v>
+        <v>-0.01210433437653748</v>
       </c>
       <c r="EH13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI13" t="n">
         <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.02266632135391921</v>
+        <v>-0.1052090213883236</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.1625280012402696</v>
+        <v>0.09921783003831809</v>
       </c>
       <c r="EL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN13" t="n">
         <v>0</v>
       </c>
       <c r="EO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.05592109575613841</v>
+        <v>-0.06078620599075187</v>
       </c>
       <c r="EQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER13" t="n">
         <v>-0</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.01969594055404902</v>
+        <v>-0.09200207356466501</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.04791468893062824</v>
+        <v>0.03668472516151875</v>
       </c>
       <c r="EU13" t="n">
         <v>-0</v>
       </c>
       <c r="EV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.1344137421487105</v>
+        <v>-0.2754521946398847</v>
       </c>
       <c r="EZ13" t="n">
         <v>0</v>
@@ -7729,52 +7729,52 @@
         <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>-0.03922102605259725</v>
+        <v>-0.01039645454523705</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.142530839603405</v>
+        <v>0.17081760624842</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
         <v>0</v>
       </c>
       <c r="FF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH13" t="n">
-        <v>0.04344902130562239</v>
+        <v>0.2230131430274353</v>
       </c>
       <c r="FI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ13" t="n">
         <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.02014927122568042</v>
+        <v>0.05403605072128495</v>
       </c>
       <c r="FL13" t="n">
-        <v>0.1489896657469541</v>
+        <v>0.1474332667557591</v>
       </c>
       <c r="FM13" t="n">
         <v>0</v>
       </c>
       <c r="FN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO13" t="n">
         <v>0</v>
       </c>
       <c r="FP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.08818304328001114</v>
+        <v>-0.1860320473429053</v>
       </c>
       <c r="FR13" t="n">
         <v>-0</v>
@@ -7783,54 +7783,54 @@
         <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>0.1847988795425745</v>
+        <v>0.05894327134887902</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.02786231107475442</v>
+        <v>0.06059053204574895</v>
       </c>
       <c r="FV13" t="n">
         <v>-0</v>
       </c>
       <c r="FW13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX13" t="n">
         <v>-0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.06853835577871248</v>
+        <v>-0.05884190041728199</v>
       </c>
       <c r="GA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0.134506346147751</v>
+        <v>0.05384216860488742</v>
       </c>
       <c r="GE13" t="n">
         <v>-0</v>
       </c>
       <c r="GF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>-0.2051387585459637</v>
+        <v>-0.1545118731368322</v>
       </c>
       <c r="B14" t="n">
-        <v>0.9124375384613524</v>
+        <v>0.2676330784304911</v>
       </c>
       <c r="C14" t="n">
         <v>-0</v>
@@ -7839,25 +7839,25 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0.09559970673416031</v>
+        <v>-0.1481766650566383</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.2608976737366263</v>
+        <v>-0.08505385776306258</v>
       </c>
       <c r="K14" t="n">
-        <v>0.8542145562941079</v>
+        <v>0.4853059301475505</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -7866,7 +7866,7 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0.02438902305585929</v>
+        <v>-0.2923514785452734</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -7881,25 +7881,25 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0.06717405162997284</v>
+        <v>0.05896411776975477</v>
       </c>
       <c r="T14" t="n">
-        <v>0.2423816441277672</v>
+        <v>0.1010682019193266</v>
       </c>
       <c r="U14" t="n">
         <v>-0</v>
       </c>
       <c r="V14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0.131084730989732</v>
+        <v>-0.05536050735899789</v>
       </c>
       <c r="X14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
@@ -7908,10 +7908,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.07838420328639652</v>
+        <v>-0.05007741383161049</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.2345068263203097</v>
+        <v>0.04275679063797296</v>
       </c>
       <c r="AD14" t="n">
         <v>-0</v>
@@ -7920,61 +7920,61 @@
         <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.0762217236553233</v>
+        <v>-0.1428623112297716</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>-0.03441851712929778</v>
+        <v>-0.06428302924220829</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.1061474602462894</v>
+        <v>0.0180671887419898</v>
       </c>
       <c r="AM14" t="n">
         <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.04092057206353567</v>
+        <v>-0.06958864609715165</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ14" t="n">
         <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT14" t="n">
-        <v>0.03466588372795239</v>
+        <v>-0.08487776352326244</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.8053532117448846</v>
+        <v>0.4230937357837591</v>
       </c>
       <c r="AV14" t="n">
         <v>-0</v>
       </c>
       <c r="AW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.3555249725514837</v>
+        <v>-0.2321552537767894</v>
       </c>
       <c r="AY14" t="n">
         <v>-0</v>
@@ -7983,25 +7983,25 @@
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
         <v>-0</v>
       </c>
       <c r="BC14" t="n">
-        <v>-0.07571441732266736</v>
+        <v>-0.05251276781472957</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.1114054041256132</v>
+        <v>0.03303900586180816</v>
       </c>
       <c r="BE14" t="n">
         <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG14" t="n">
-        <v>-0.2020689909903703</v>
+        <v>-0.003220739727159529</v>
       </c>
       <c r="BH14" t="n">
         <v>0</v>
@@ -8010,16 +8010,16 @@
         <v>-0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL14" t="n">
-        <v>0.02971428210900054</v>
+        <v>0.03248285024384167</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.009203241287896593</v>
+        <v>0.1544978163378415</v>
       </c>
       <c r="BN14" t="n">
         <v>-0</v>
@@ -8028,7 +8028,7 @@
         <v>-0</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.1164845846802259</v>
+        <v>0.1489538366148972</v>
       </c>
       <c r="BQ14" t="n">
         <v>-0</v>
@@ -8043,25 +8043,25 @@
         <v>-0</v>
       </c>
       <c r="BU14" t="n">
-        <v>0.0519921841821125</v>
+        <v>0.02672091150261923</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.4811297002840509</v>
+        <v>0.2270057378461978</v>
       </c>
       <c r="BW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.1125230737979435</v>
+        <v>-0.06708614756204359</v>
       </c>
       <c r="BZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB14" t="n">
         <v>-0</v>
@@ -8070,49 +8070,49 @@
         <v>0</v>
       </c>
       <c r="CD14" t="n">
-        <v>0.02575665785360905</v>
+        <v>0.05779930130685788</v>
       </c>
       <c r="CE14" t="n">
-        <v>-0.2237454737574341</v>
+        <v>-0.06579471359757504</v>
       </c>
       <c r="CF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG14" t="n">
         <v>-0</v>
       </c>
       <c r="CH14" t="n">
-        <v>-0.05867831642146935</v>
+        <v>0.08883572334961308</v>
       </c>
       <c r="CI14" t="n">
         <v>-0</v>
       </c>
       <c r="CJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM14" t="n">
-        <v>-0.1809394681573626</v>
+        <v>-0.06321007616374089</v>
       </c>
       <c r="CN14" t="n">
-        <v>-0.05504619581608389</v>
+        <v>-0.1538095400990202</v>
       </c>
       <c r="CO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ14" t="n">
-        <v>-0.1248711127301497</v>
+        <v>0.001055746414048001</v>
       </c>
       <c r="CR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS14" t="n">
         <v>-0</v>
@@ -8121,13 +8121,13 @@
         <v>-0</v>
       </c>
       <c r="CU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV14" t="n">
-        <v>0.009860383284629693</v>
+        <v>0.02354788011593569</v>
       </c>
       <c r="CW14" t="n">
-        <v>-0.2377696976547401</v>
+        <v>-0.06854038524459354</v>
       </c>
       <c r="CX14" t="n">
         <v>-0</v>
@@ -8136,121 +8136,121 @@
         <v>0</v>
       </c>
       <c r="CZ14" t="n">
-        <v>-0.06914893628880042</v>
+        <v>0.03527535978967526</v>
       </c>
       <c r="DA14" t="n">
         <v>0</v>
       </c>
       <c r="DB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC14" t="n">
         <v>0</v>
       </c>
       <c r="DD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE14" t="n">
-        <v>-0.03543241183969065</v>
+        <v>0.03585925575420546</v>
       </c>
       <c r="DF14" t="n">
-        <v>-0.2521827491062154</v>
+        <v>-0.1735236189725069</v>
       </c>
       <c r="DG14" t="n">
         <v>-0</v>
       </c>
       <c r="DH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI14" t="n">
-        <v>-0.06508860096348637</v>
+        <v>-0.1221576772280661</v>
       </c>
       <c r="DJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK14" t="n">
         <v>-0</v>
       </c>
       <c r="DL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN14" t="n">
-        <v>-0.05180754205119136</v>
+        <v>-0.01156649613224173</v>
       </c>
       <c r="DO14" t="n">
-        <v>-0.1362012624299459</v>
+        <v>0.003454180601525676</v>
       </c>
       <c r="DP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR14" t="n">
-        <v>0.005750825675808329</v>
+        <v>-0.06008237696624104</v>
       </c>
       <c r="DS14" t="n">
         <v>-0</v>
       </c>
       <c r="DT14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.006464306138407768</v>
+        <v>0.1016655445420255</v>
       </c>
       <c r="DX14" t="n">
-        <v>-0.1912935051681879</v>
+        <v>-0.06753968223285463</v>
       </c>
       <c r="DY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA14" t="n">
-        <v>-0.06148877020670131</v>
+        <v>-0.05745885510374543</v>
       </c>
       <c r="EB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC14" t="n">
         <v>-0</v>
       </c>
       <c r="ED14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF14" t="n">
-        <v>-0.09244789017948719</v>
+        <v>-0.1260474683565638</v>
       </c>
       <c r="EG14" t="n">
-        <v>-0.1114158981032856</v>
+        <v>0.002271731495980363</v>
       </c>
       <c r="EH14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI14" t="n">
         <v>-0</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.05073510940896747</v>
+        <v>0.0121519383076786</v>
       </c>
       <c r="EK14" t="n">
         <v>-0</v>
       </c>
       <c r="EL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM14" t="n">
         <v>-0</v>
@@ -8259,37 +8259,37 @@
         <v>-0</v>
       </c>
       <c r="EO14" t="n">
-        <v>-0.03670091136969254</v>
+        <v>-0.07309581133314566</v>
       </c>
       <c r="EP14" t="n">
-        <v>-0.1775825467648408</v>
+        <v>0.039855041409178</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER14" t="n">
         <v>-0</v>
       </c>
       <c r="ES14" t="n">
-        <v>-0.1659908270553308</v>
+        <v>0.01972227041551767</v>
       </c>
       <c r="ET14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW14" t="n">
         <v>0</v>
       </c>
       <c r="EX14" t="n">
-        <v>-0.007449497942732738</v>
+        <v>0.0470797824201409</v>
       </c>
       <c r="EY14" t="n">
-        <v>-0.2369197919900651</v>
+        <v>-0.1117152288401225</v>
       </c>
       <c r="EZ14" t="n">
         <v>0</v>
@@ -8298,25 +8298,25 @@
         <v>-0</v>
       </c>
       <c r="FB14" t="n">
-        <v>-0.1154745563659354</v>
+        <v>0.04991009413065339</v>
       </c>
       <c r="FC14" t="n">
         <v>-0</v>
       </c>
       <c r="FD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG14" t="n">
-        <v>-0.02432431489100056</v>
+        <v>0.0121501455000056</v>
       </c>
       <c r="FH14" t="n">
-        <v>-0.03658066506039972</v>
+        <v>0.1099286456171329</v>
       </c>
       <c r="FI14" t="n">
         <v>-0</v>
@@ -8325,10 +8325,10 @@
         <v>-0</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.01636569070045835</v>
+        <v>-0.1434242209971183</v>
       </c>
       <c r="FL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM14" t="n">
         <v>0</v>
@@ -8340,25 +8340,25 @@
         <v>0</v>
       </c>
       <c r="FP14" t="n">
-        <v>-0.1219778731001157</v>
+        <v>-0.003156392708718107</v>
       </c>
       <c r="FQ14" t="n">
-        <v>-0.2285094271733714</v>
+        <v>-0.05350218643870392</v>
       </c>
       <c r="FR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS14" t="n">
         <v>-0</v>
       </c>
       <c r="FT14" t="n">
-        <v>-0.213154584523489</v>
+        <v>0.2307292274194992</v>
       </c>
       <c r="FU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW14" t="n">
         <v>-0</v>
@@ -8367,22 +8367,22 @@
         <v>-0</v>
       </c>
       <c r="FY14" t="n">
-        <v>-0.183060046086167</v>
+        <v>0.0476247510073397</v>
       </c>
       <c r="FZ14" t="n">
-        <v>-0.0975203873225194</v>
+        <v>-0.04734341710804203</v>
       </c>
       <c r="GA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB14" t="n">
         <v>-0</v>
       </c>
       <c r="GC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE14" t="n">
         <v>-0</v>
@@ -8391,7 +8391,7 @@
         <v>-0</v>
       </c>
       <c r="GG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -8399,7 +8399,7 @@
         <v>0</v>
       </c>
       <c r="B15" t="n">
-        <v>0.4710912653488064</v>
+        <v>0.04750403504362768</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -8408,7 +8408,7 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2046901961649735</v>
+        <v>-0.01152476452123723</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -8417,7 +8417,7 @@
         <v>-0</v>
       </c>
       <c r="H15" t="n">
-        <v>0.007853621829637074</v>
+        <v>-0.006227520682417899</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -8426,7 +8426,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.4057165749466082</v>
+        <v>0.06559111304565771</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -8435,25 +8435,25 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.2176154284123121</v>
+        <v>-0.03108822869611217</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.06142059858944812</v>
+        <v>-0.02119450595699542</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1158394751770186</v>
+        <v>0.009353524773246961</v>
       </c>
       <c r="U15" t="n">
         <v>-0</v>
@@ -8462,16 +8462,16 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.02580586041198331</v>
+        <v>0.00667415320804738</v>
       </c>
       <c r="X15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>-0.04083375595604836</v>
+        <v>-0.001429725339796455</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -8480,7 +8480,7 @@
         <v>-0</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.1758035736317312</v>
+        <v>-0.005670446652735367</v>
       </c>
       <c r="AD15" t="n">
         <v>-0</v>
@@ -8489,16 +8489,16 @@
         <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>-0.1224727093546701</v>
+        <v>-0.01732037951152134</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>-0.01161982137730038</v>
+        <v>-0.001049114950267168</v>
       </c>
       <c r="AJ15" t="n">
         <v>-0</v>
@@ -8507,34 +8507,34 @@
         <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.0740738657735347</v>
+        <v>0.01038964426626868</v>
       </c>
       <c r="AM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
         <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0.02949696275775219</v>
+        <v>0.01166345803743555</v>
       </c>
       <c r="AP15" t="n">
         <v>0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR15" t="n">
-        <v>-0.05533196444654851</v>
+        <v>-0.002391467775424224</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT15" t="n">
         <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.417412770217926</v>
+        <v>0.0465065607303952</v>
       </c>
       <c r="AV15" t="n">
         <v>-0</v>
@@ -8543,25 +8543,25 @@
         <v>-0</v>
       </c>
       <c r="AX15" t="n">
-        <v>0.03686887244178801</v>
+        <v>0.004119237429666606</v>
       </c>
       <c r="AY15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AZ15" t="n">
         <v>-0</v>
       </c>
       <c r="BA15" t="n">
-        <v>0.03588582705249777</v>
+        <v>-0.005832471921394631</v>
       </c>
       <c r="BB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC15" t="n">
         <v>0</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.08272696292415983</v>
+        <v>-0.002592212366552015</v>
       </c>
       <c r="BE15" t="n">
         <v>0</v>
@@ -8570,16 +8570,16 @@
         <v>0</v>
       </c>
       <c r="BG15" t="n">
-        <v>-0.1931966193130564</v>
+        <v>-0.01900734120933965</v>
       </c>
       <c r="BH15" t="n">
         <v>0</v>
       </c>
       <c r="BI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ15" t="n">
-        <v>-0.05162487017478355</v>
+        <v>-0.001657893609107438</v>
       </c>
       <c r="BK15" t="n">
         <v>0</v>
@@ -8588,7 +8588,7 @@
         <v>-0</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.05930893196124712</v>
+        <v>-0.004227909878651247</v>
       </c>
       <c r="BN15" t="n">
         <v>-0</v>
@@ -8597,43 +8597,43 @@
         <v>-0</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.0776362319171847</v>
+        <v>0.02531414881515537</v>
       </c>
       <c r="BQ15" t="n">
         <v>-0</v>
       </c>
       <c r="BR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS15" t="n">
-        <v>0.02003671831839036</v>
+        <v>0.01022129283560076</v>
       </c>
       <c r="BT15" t="n">
         <v>-0</v>
       </c>
       <c r="BU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.2501848770920686</v>
+        <v>0.03481685035291234</v>
       </c>
       <c r="BW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX15" t="n">
         <v>-0</v>
       </c>
       <c r="BY15" t="n">
-        <v>-0.008919011298759685</v>
+        <v>0.01261035183572966</v>
       </c>
       <c r="BZ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA15" t="n">
         <v>-0</v>
       </c>
       <c r="CB15" t="n">
-        <v>0.0298916123720695</v>
+        <v>-0.004200449449274435</v>
       </c>
       <c r="CC15" t="n">
         <v>0</v>
@@ -8642,16 +8642,16 @@
         <v>-0</v>
       </c>
       <c r="CE15" t="n">
-        <v>-0.106098617200308</v>
+        <v>-0.01878916696538281</v>
       </c>
       <c r="CF15" t="n">
         <v>-0</v>
       </c>
       <c r="CG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.02358281400349414</v>
+        <v>0.004552869431906995</v>
       </c>
       <c r="CI15" t="n">
         <v>-0</v>
@@ -8660,88 +8660,88 @@
         <v>0</v>
       </c>
       <c r="CK15" t="n">
-        <v>-0.004374166536911765</v>
+        <v>0.004200929497797707</v>
       </c>
       <c r="CL15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM15" t="n">
         <v>0</v>
       </c>
       <c r="CN15" t="n">
-        <v>-0.03832333870684061</v>
+        <v>-0.01815880388952718</v>
       </c>
       <c r="CO15" t="n">
         <v>-0</v>
       </c>
       <c r="CP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ15" t="n">
-        <v>-0.1267692116350717</v>
+        <v>-0.003454804125876427</v>
       </c>
       <c r="CR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS15" t="n">
         <v>-0</v>
       </c>
       <c r="CT15" t="n">
-        <v>-0.001998128510986145</v>
+        <v>0.002042386350667684</v>
       </c>
       <c r="CU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV15" t="n">
         <v>0</v>
       </c>
       <c r="CW15" t="n">
-        <v>-0.09616160862667707</v>
+        <v>-0.01913021926106008</v>
       </c>
       <c r="CX15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.004335682047606522</v>
+        <v>0.004008916695394294</v>
       </c>
       <c r="DA15" t="n">
         <v>0</v>
       </c>
       <c r="DB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC15" t="n">
-        <v>-0.01177733850943323</v>
+        <v>0.004751766761911121</v>
       </c>
       <c r="DD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>-0.1721383722102683</v>
+        <v>-0.01256738438340767</v>
       </c>
       <c r="DG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.08682120371039685</v>
+        <v>-0.01026316347408058</v>
       </c>
       <c r="DJ15" t="n">
         <v>-0</v>
       </c>
       <c r="DK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL15" t="n">
-        <v>-0.04598328725943202</v>
+        <v>-0.003883770180549891</v>
       </c>
       <c r="DM15" t="n">
         <v>-0</v>
@@ -8750,61 +8750,61 @@
         <v>-0</v>
       </c>
       <c r="DO15" t="n">
-        <v>-0.006769509984030727</v>
+        <v>-0.001725789273272847</v>
       </c>
       <c r="DP15" t="n">
         <v>-0</v>
       </c>
       <c r="DQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DR15" t="n">
-        <v>-0.05484088096683114</v>
+        <v>0.0001720268049204066</v>
       </c>
       <c r="DS15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT15" t="n">
         <v>0</v>
       </c>
       <c r="DU15" t="n">
-        <v>-0.004638283624451488</v>
+        <v>0.007424053877500785</v>
       </c>
       <c r="DV15" t="n">
         <v>0</v>
       </c>
       <c r="DW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX15" t="n">
-        <v>-0.053431797233202</v>
+        <v>-0.01179921238201746</v>
       </c>
       <c r="DY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EA15" t="n">
-        <v>-0.0693271317600051</v>
+        <v>-0.004781230424296875</v>
       </c>
       <c r="EB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC15" t="n">
         <v>-0</v>
       </c>
       <c r="ED15" t="n">
-        <v>0.04073147701627769</v>
+        <v>-0.004311376754400293</v>
       </c>
       <c r="EE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF15" t="n">
         <v>-0</v>
       </c>
       <c r="EG15" t="n">
-        <v>-0.08996777184590696</v>
+        <v>-0.003982687156439711</v>
       </c>
       <c r="EH15" t="n">
         <v>0</v>
@@ -8813,7 +8813,7 @@
         <v>0</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.07821412132433167</v>
+        <v>-0.0002253027421724809</v>
       </c>
       <c r="EK15" t="n">
         <v>-0</v>
@@ -8822,52 +8822,52 @@
         <v>-0</v>
       </c>
       <c r="EM15" t="n">
-        <v>-0.02916394622604921</v>
+        <v>0.001919621756696526</v>
       </c>
       <c r="EN15" t="n">
         <v>-0</v>
       </c>
       <c r="EO15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP15" t="n">
-        <v>-0.05844977158481841</v>
+        <v>-0.01812917592470591</v>
       </c>
       <c r="EQ15" t="n">
         <v>0</v>
       </c>
       <c r="ER15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES15" t="n">
-        <v>-0.01624527038153707</v>
+        <v>0.001087493525807502</v>
       </c>
       <c r="ET15" t="n">
         <v>-0</v>
       </c>
       <c r="EU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV15" t="n">
-        <v>-0.001420375838872451</v>
+        <v>0.005416603350901809</v>
       </c>
       <c r="EW15" t="n">
         <v>0</v>
       </c>
       <c r="EX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY15" t="n">
-        <v>-0.1005848162548132</v>
+        <v>-0.02134938415830141</v>
       </c>
       <c r="EZ15" t="n">
         <v>-0</v>
       </c>
       <c r="FA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB15" t="n">
-        <v>-0.01174953454441455</v>
+        <v>-0.00034699044439596</v>
       </c>
       <c r="FC15" t="n">
         <v>-0</v>
@@ -8876,16 +8876,16 @@
         <v>-0</v>
       </c>
       <c r="FE15" t="n">
-        <v>-0.001356867073221091</v>
+        <v>0.00385004968224961</v>
       </c>
       <c r="FF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.04827900316176969</v>
+        <v>0.01244701962366924</v>
       </c>
       <c r="FI15" t="n">
         <v>-0</v>
@@ -8894,16 +8894,16 @@
         <v>-0</v>
       </c>
       <c r="FK15" t="n">
-        <v>-0.05296542861680146</v>
+        <v>-0.00636668202867633</v>
       </c>
       <c r="FL15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM15" t="n">
         <v>0</v>
       </c>
       <c r="FN15" t="n">
-        <v>0.02024340353452489</v>
+        <v>0.002319885756403633</v>
       </c>
       <c r="FO15" t="n">
         <v>-0</v>
@@ -8912,7 +8912,7 @@
         <v>-0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>-0.01543824415344748</v>
+        <v>-0.01003889983562052</v>
       </c>
       <c r="FR15" t="n">
         <v>-0</v>
@@ -8921,25 +8921,25 @@
         <v>-0</v>
       </c>
       <c r="FT15" t="n">
-        <v>0.0237427957797768</v>
+        <v>-0.0009674974583359102</v>
       </c>
       <c r="FU15" t="n">
         <v>0</v>
       </c>
       <c r="FV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW15" t="n">
-        <v>0.002923557205233586</v>
+        <v>0.002266053931683138</v>
       </c>
       <c r="FX15" t="n">
         <v>-0</v>
       </c>
       <c r="FY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>-0.07464997642407588</v>
+        <v>-0.01254348978374567</v>
       </c>
       <c r="GA15" t="n">
         <v>0</v>
@@ -8951,16 +8951,16 @@
         <v>0</v>
       </c>
       <c r="GD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE15" t="n">
         <v>-0</v>
       </c>
       <c r="GF15" t="n">
-        <v>-0.05652794587616708</v>
+        <v>-0.008276291881066981</v>
       </c>
       <c r="GG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -8968,25 +8968,25 @@
         <v>0</v>
       </c>
       <c r="B16" t="n">
-        <v>0.2702912838627323</v>
+        <v>0.01720368434882814</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.1054934075148222</v>
+        <v>-0.004249098980209451</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>0.004576726381069439</v>
+        <v>0.001745391301487269</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -8995,22 +8995,22 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.2198853770278497</v>
+        <v>0.02588829852052166</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.08854673173902292</v>
+        <v>-0.004364790952508634</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.04984873405372747</v>
+        <v>-0.007156527186163708</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -9022,97 +9022,97 @@
         <v>-0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.03220554537904734</v>
+        <v>0.006904550744184189</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.01042586294037256</v>
+        <v>0.003179664136612994</v>
       </c>
       <c r="V16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0.04606893033899524</v>
+        <v>0.0110693612234197</v>
       </c>
       <c r="X16" t="n">
         <v>-0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
         <v>-0</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.09206668992985011</v>
+        <v>-0.002168518899565786</v>
       </c>
       <c r="AD16" t="n">
-        <v>0.00486552686971979</v>
+        <v>-0.003440795366281273</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.01090809188192679</v>
+        <v>-0.0255225641528496</v>
       </c>
       <c r="AG16" t="n">
         <v>-0</v>
       </c>
       <c r="AH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ16" t="n">
         <v>-0</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.03976156188317363</v>
+        <v>0.0120610743519694</v>
       </c>
       <c r="AM16" t="n">
-        <v>-0.02403898915860778</v>
+        <v>0.002392856554825687</v>
       </c>
       <c r="AN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.01310458162085699</v>
+        <v>0.004810597864078951</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS16" t="n">
         <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.2066633692580593</v>
+        <v>0.0307816606984656</v>
       </c>
       <c r="AV16" t="n">
-        <v>-0.06159425373034457</v>
+        <v>0.006252776753979102</v>
       </c>
       <c r="AW16" t="n">
         <v>-0</v>
       </c>
       <c r="AX16" t="n">
-        <v>0.04222238100293722</v>
+        <v>-0.003124731114660065</v>
       </c>
       <c r="AY16" t="n">
         <v>0</v>
@@ -9127,22 +9127,22 @@
         <v>0</v>
       </c>
       <c r="BC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.07701932569997068</v>
+        <v>-0.004373178507736501</v>
       </c>
       <c r="BE16" t="n">
-        <v>-0.0669373926249021</v>
+        <v>-0.006855630958265758</v>
       </c>
       <c r="BF16" t="n">
         <v>0</v>
       </c>
       <c r="BG16" t="n">
-        <v>-0.08326232115916296</v>
+        <v>-0.01261051661354017</v>
       </c>
       <c r="BH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI16" t="n">
         <v>-0</v>
@@ -9151,28 +9151,28 @@
         <v>0</v>
       </c>
       <c r="BK16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.03922143299574027</v>
+        <v>0.004447583485541588</v>
       </c>
       <c r="BN16" t="n">
-        <v>-0.04610431381525728</v>
+        <v>0.001031949328631171</v>
       </c>
       <c r="BO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP16" t="n">
-        <v>0.02677604891025485</v>
+        <v>0.004019130315394534</v>
       </c>
       <c r="BQ16" t="n">
         <v>-0</v>
       </c>
       <c r="BR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS16" t="n">
         <v>-0</v>
@@ -9184,49 +9184,49 @@
         <v>-0</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.08475183383924009</v>
+        <v>0.02401321361906027</v>
       </c>
       <c r="BW16" t="n">
-        <v>-0.1075671911332393</v>
+        <v>0.005966791903232453</v>
       </c>
       <c r="BX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY16" t="n">
-        <v>0.02845306268292037</v>
+        <v>0.01136411729333206</v>
       </c>
       <c r="BZ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB16" t="n">
         <v>0</v>
       </c>
       <c r="CC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE16" t="n">
-        <v>-0.06244234883672542</v>
+        <v>-0.006447416688704963</v>
       </c>
       <c r="CF16" t="n">
-        <v>-0.00107544301266719</v>
+        <v>0.002878571386670605</v>
       </c>
       <c r="CG16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH16" t="n">
-        <v>-0.00613808407776136</v>
+        <v>-0.000632221251589238</v>
       </c>
       <c r="CI16" t="n">
         <v>-0</v>
       </c>
       <c r="CJ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK16" t="n">
         <v>-0</v>
@@ -9238,43 +9238,43 @@
         <v>0</v>
       </c>
       <c r="CN16" t="n">
-        <v>-0.01049449992626484</v>
+        <v>-0.01768189000364896</v>
       </c>
       <c r="CO16" t="n">
-        <v>-0.002130780132696616</v>
+        <v>-0.003199343869279261</v>
       </c>
       <c r="CP16" t="n">
         <v>-0</v>
       </c>
       <c r="CQ16" t="n">
-        <v>0.007917146017830289</v>
+        <v>0.006451779314546929</v>
       </c>
       <c r="CR16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS16" t="n">
         <v>-0</v>
       </c>
       <c r="CT16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW16" t="n">
-        <v>-0.05392090265536812</v>
+        <v>-0.00623393129178188</v>
       </c>
       <c r="CX16" t="n">
-        <v>-0.0115714729735867</v>
+        <v>0.002350774195818458</v>
       </c>
       <c r="CY16" t="n">
         <v>0</v>
       </c>
       <c r="CZ16" t="n">
-        <v>-0.02127049528958345</v>
+        <v>-0.002737054948293129</v>
       </c>
       <c r="DA16" t="n">
         <v>0</v>
@@ -9292,22 +9292,22 @@
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>-0.06621369962480785</v>
+        <v>-0.00899012737117927</v>
       </c>
       <c r="DG16" t="n">
-        <v>0.002337616543583512</v>
+        <v>0.005776947060593142</v>
       </c>
       <c r="DH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI16" t="n">
-        <v>-0.01364576154070779</v>
+        <v>-0.007852642902047241</v>
       </c>
       <c r="DJ16" t="n">
         <v>-0</v>
       </c>
       <c r="DK16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL16" t="n">
         <v>0</v>
@@ -9316,19 +9316,19 @@
         <v>-0</v>
       </c>
       <c r="DN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO16" t="n">
-        <v>-0.008046058618139063</v>
+        <v>-0.0006179071979501828</v>
       </c>
       <c r="DP16" t="n">
-        <v>-0.03153246575185505</v>
+        <v>-0.006042807845029852</v>
       </c>
       <c r="DQ16" t="n">
         <v>0</v>
       </c>
       <c r="DR16" t="n">
-        <v>0.01899972062022873</v>
+        <v>0.00528465987624425</v>
       </c>
       <c r="DS16" t="n">
         <v>-0</v>
@@ -9340,25 +9340,25 @@
         <v>-0</v>
       </c>
       <c r="DV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX16" t="n">
-        <v>-0.07602019564491927</v>
+        <v>-0.01216602204072815</v>
       </c>
       <c r="DY16" t="n">
-        <v>0.009032779438749956</v>
+        <v>-0.0002764544474909292</v>
       </c>
       <c r="DZ16" t="n">
         <v>-0</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.0052755013053967</v>
+        <v>-0.003540420513814817</v>
       </c>
       <c r="EB16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC16" t="n">
         <v>-0</v>
@@ -9367,25 +9367,25 @@
         <v>0</v>
       </c>
       <c r="EE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF16" t="n">
         <v>0</v>
       </c>
       <c r="EG16" t="n">
-        <v>-0.02881903082012044</v>
+        <v>0.0005090965068074692</v>
       </c>
       <c r="EH16" t="n">
-        <v>0.0006312915280258072</v>
+        <v>0.004520851244013494</v>
       </c>
       <c r="EI16" t="n">
         <v>0</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.02096486096636332</v>
+        <v>-0.004473759387044331</v>
       </c>
       <c r="EK16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL16" t="n">
         <v>-0</v>
@@ -9394,49 +9394,49 @@
         <v>-0</v>
       </c>
       <c r="EN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO16" t="n">
         <v>0</v>
       </c>
       <c r="EP16" t="n">
-        <v>-0.05027865717491811</v>
+        <v>-0.006458989734918708</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0.03099546052736537</v>
+        <v>-0.001161361127926933</v>
       </c>
       <c r="ER16" t="n">
         <v>-0</v>
       </c>
       <c r="ES16" t="n">
-        <v>-0.01802245750474361</v>
+        <v>0.001596336496542843</v>
       </c>
       <c r="ET16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW16" t="n">
         <v>-0</v>
       </c>
       <c r="EX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY16" t="n">
-        <v>-0.05680942620833573</v>
+        <v>-0.008449850551760304</v>
       </c>
       <c r="EZ16" t="n">
-        <v>-0.003330138602024208</v>
+        <v>0.002036228193397048</v>
       </c>
       <c r="FA16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB16" t="n">
-        <v>-0.007123559294047027</v>
+        <v>-0.001580360933198314</v>
       </c>
       <c r="FC16" t="n">
         <v>-0</v>
@@ -9445,7 +9445,7 @@
         <v>-0</v>
       </c>
       <c r="FE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF16" t="n">
         <v>-0</v>
@@ -9454,46 +9454,46 @@
         <v>-0</v>
       </c>
       <c r="FH16" t="n">
-        <v>-0.01500028279327427</v>
+        <v>-0.001241084812437704</v>
       </c>
       <c r="FI16" t="n">
-        <v>0.004736339562536831</v>
+        <v>0.00725616506002589</v>
       </c>
       <c r="FJ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FK16" t="n">
-        <v>0.06053773106781415</v>
+        <v>0.006402197172839071</v>
       </c>
       <c r="FL16" t="n">
         <v>-0</v>
       </c>
       <c r="FM16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ16" t="n">
-        <v>-0.01169703809469666</v>
+        <v>-0.003290179333000005</v>
       </c>
       <c r="FR16" t="n">
-        <v>0.03839508970272475</v>
+        <v>-0.002366205881505173</v>
       </c>
       <c r="FS16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FT16" t="n">
-        <v>0.02286639539670951</v>
+        <v>0.007760334300738703</v>
       </c>
       <c r="FU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FV16" t="n">
         <v>-0</v>
@@ -9502,31 +9502,31 @@
         <v>0</v>
       </c>
       <c r="FX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ16" t="n">
-        <v>0.02108894758841711</v>
+        <v>-0.009776494087160088</v>
       </c>
       <c r="GA16" t="n">
-        <v>-0.009871620272156469</v>
+        <v>-0.003142297342036255</v>
       </c>
       <c r="GB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE16" t="n">
         <v>-0</v>
       </c>
       <c r="GF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG16" t="n">
         <v>0</v>
@@ -10672,10 +10672,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>-0.1030235892895528</v>
+        <v>-0.1724544283576091</v>
       </c>
       <c r="B19" t="n">
-        <v>0.8285283075101392</v>
+        <v>0.3497355738485313</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -10684,7 +10684,7 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2414521541289058</v>
+        <v>-0.2182485734689576</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -10699,19 +10699,19 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.158392189651844</v>
+        <v>-0.1209902380142184</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6193755452703801</v>
+        <v>0.4103544720483975</v>
       </c>
       <c r="L19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2808138460182866</v>
+        <v>-0.2936579907951176</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -10726,49 +10726,49 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.006424122077153116</v>
+        <v>0.05664052558018271</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1498721296715293</v>
+        <v>0.03504987421086276</v>
       </c>
       <c r="U19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.03875980000131445</v>
+        <v>-0.1207150189064193</v>
       </c>
       <c r="X19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
         <v>-0</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.04265992508014846</v>
+        <v>-0.03328567854827205</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.1782433572558032</v>
+        <v>0.07627019968859192</v>
       </c>
       <c r="AD19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
         <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>-0.07028858481827339</v>
+        <v>-0.2828981792910091</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH19" t="n">
         <v>-0</v>
@@ -10777,49 +10777,49 @@
         <v>-0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>-0.05360548081793667</v>
+        <v>-0.0447055318596386</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.1033713700661508</v>
+        <v>0.05471570525175179</v>
       </c>
       <c r="AM19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
         <v>0</v>
       </c>
       <c r="AO19" t="n">
-        <v>-0.0454916496613532</v>
+        <v>-0.2499143150325506</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR19" t="n">
         <v>-0</v>
       </c>
       <c r="AS19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT19" t="n">
-        <v>-0.01297963833460063</v>
+        <v>0.02523884405473992</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.5802687936147327</v>
+        <v>0.4569562082066596</v>
       </c>
       <c r="AV19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.1457918691933472</v>
+        <v>-0.4751923409512532</v>
       </c>
       <c r="AY19" t="n">
         <v>0</v>
@@ -10831,22 +10831,22 @@
         <v>-0</v>
       </c>
       <c r="BB19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>-0.02951729368028931</v>
+        <v>-0.03762417760083699</v>
       </c>
       <c r="BD19" t="n">
-        <v>0.1300787652963142</v>
+        <v>0.1658591745939283</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF19" t="n">
         <v>0</v>
       </c>
       <c r="BG19" t="n">
-        <v>-0.2417319048519269</v>
+        <v>0.1585465887885798</v>
       </c>
       <c r="BH19" t="n">
         <v>0</v>
@@ -10855,31 +10855,31 @@
         <v>-0</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK19" t="n">
         <v>0</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.0233835471354444</v>
+        <v>0.0186575058702719</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.1228547145237824</v>
+        <v>0.3655730470907456</v>
       </c>
       <c r="BN19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO19" t="n">
         <v>-0</v>
       </c>
       <c r="BP19" t="n">
-        <v>0.1202583028247091</v>
+        <v>0.1934853464277761</v>
       </c>
       <c r="BQ19" t="n">
         <v>-0</v>
       </c>
       <c r="BR19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS19" t="n">
         <v>-0</v>
@@ -10888,22 +10888,22 @@
         <v>-0</v>
       </c>
       <c r="BU19" t="n">
-        <v>0.009498726418643974</v>
+        <v>0.04816688733292988</v>
       </c>
       <c r="BV19" t="n">
-        <v>0.3399335900399296</v>
+        <v>0.1870928140999293</v>
       </c>
       <c r="BW19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY19" t="n">
-        <v>0.0384426626729837</v>
+        <v>-0.1559634797334668</v>
       </c>
       <c r="BZ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA19" t="n">
         <v>-0</v>
@@ -10915,49 +10915,49 @@
         <v>0</v>
       </c>
       <c r="CD19" t="n">
-        <v>0.01698499269037195</v>
+        <v>0.06455499581674043</v>
       </c>
       <c r="CE19" t="n">
-        <v>-0.1291503228567244</v>
+        <v>-0.03521308150385833</v>
       </c>
       <c r="CF19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG19" t="n">
         <v>-0</v>
       </c>
       <c r="CH19" t="n">
-        <v>0.009055596932915544</v>
+        <v>0.09729488853111798</v>
       </c>
       <c r="CI19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM19" t="n">
-        <v>-0.1105943280113055</v>
+        <v>-0.1496107041807438</v>
       </c>
       <c r="CN19" t="n">
-        <v>-0.05736224547522696</v>
+        <v>-0.3741337283609932</v>
       </c>
       <c r="CO19" t="n">
         <v>-0</v>
       </c>
       <c r="CP19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ19" t="n">
-        <v>-0.2526563094681473</v>
+        <v>-0.02247031975865301</v>
       </c>
       <c r="CR19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS19" t="n">
         <v>-0</v>
@@ -10966,94 +10966,94 @@
         <v>0</v>
       </c>
       <c r="CU19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV19" t="n">
-        <v>0.009351487353691694</v>
+        <v>0.03587927350478305</v>
       </c>
       <c r="CW19" t="n">
-        <v>-0.1144743467087338</v>
+        <v>-0.03092382273199725</v>
       </c>
       <c r="CX19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY19" t="n">
         <v>0</v>
       </c>
       <c r="CZ19" t="n">
-        <v>-0.006459107078569082</v>
+        <v>0.03244655608629068</v>
       </c>
       <c r="DA19" t="n">
         <v>0</v>
       </c>
       <c r="DB19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD19" t="n">
         <v>0</v>
       </c>
       <c r="DE19" t="n">
-        <v>-0.03297340390898228</v>
+        <v>-0.04909933523398274</v>
       </c>
       <c r="DF19" t="n">
-        <v>-0.2334527562169257</v>
+        <v>-0.1761771799870934</v>
       </c>
       <c r="DG19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH19" t="n">
         <v>-0</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.08858409009080577</v>
+        <v>-0.04084027060838166</v>
       </c>
       <c r="DJ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL19" t="n">
         <v>0</v>
       </c>
       <c r="DM19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN19" t="n">
-        <v>-0.01577137947316656</v>
+        <v>-0.09453064385128317</v>
       </c>
       <c r="DO19" t="n">
-        <v>-0.02644150260474605</v>
+        <v>-0.008941953716941444</v>
       </c>
       <c r="DP19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ19" t="n">
         <v>0</v>
       </c>
       <c r="DR19" t="n">
-        <v>-0.0400221375990043</v>
+        <v>-0.07740781177764539</v>
       </c>
       <c r="DS19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT19" t="n">
         <v>0</v>
       </c>
       <c r="DU19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW19" t="n">
-        <v>-0.006912324072061461</v>
+        <v>0.08439661343924672</v>
       </c>
       <c r="DX19" t="n">
-        <v>-0.1500722425223427</v>
+        <v>-0.01707931940946061</v>
       </c>
       <c r="DY19" t="n">
         <v>0</v>
@@ -11062,34 +11062,34 @@
         <v>-0</v>
       </c>
       <c r="EA19" t="n">
-        <v>0.08106793992968868</v>
+        <v>-0.1472981731439371</v>
       </c>
       <c r="EB19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC19" t="n">
         <v>0</v>
       </c>
       <c r="ED19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE19" t="n">
         <v>-0</v>
       </c>
       <c r="EF19" t="n">
-        <v>-0.0189091154871905</v>
+        <v>-0.00359652150273712</v>
       </c>
       <c r="EG19" t="n">
-        <v>-0.08988636023061211</v>
+        <v>0.1100084722540024</v>
       </c>
       <c r="EH19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI19" t="n">
         <v>-0</v>
       </c>
       <c r="EJ19" t="n">
-        <v>0.1030622664043265</v>
+        <v>-0.005568995139428629</v>
       </c>
       <c r="EK19" t="n">
         <v>-0</v>
@@ -11098,112 +11098,112 @@
         <v>-0</v>
       </c>
       <c r="EM19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN19" t="n">
         <v>-0</v>
       </c>
       <c r="EO19" t="n">
-        <v>-0.02072866488113738</v>
+        <v>-0.03771390977021172</v>
       </c>
       <c r="EP19" t="n">
-        <v>-0.1036150086209641</v>
+        <v>0.03845791133345811</v>
       </c>
       <c r="EQ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER19" t="n">
         <v>-0</v>
       </c>
       <c r="ES19" t="n">
-        <v>-0.07121160915617848</v>
+        <v>0.07095853592339588</v>
       </c>
       <c r="ET19" t="n">
         <v>-0</v>
       </c>
       <c r="EU19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX19" t="n">
-        <v>-0.004296178833598676</v>
+        <v>0.04161022717142283</v>
       </c>
       <c r="EY19" t="n">
-        <v>-0.1242077578541294</v>
+        <v>-0.09230527735011579</v>
       </c>
       <c r="EZ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA19" t="n">
         <v>-0</v>
       </c>
       <c r="FB19" t="n">
-        <v>-0.02109431844777622</v>
+        <v>0.03810723047255326</v>
       </c>
       <c r="FC19" t="n">
         <v>-0</v>
       </c>
       <c r="FD19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG19" t="n">
-        <v>-0.01183042190480619</v>
+        <v>0.02988545551729768</v>
       </c>
       <c r="FH19" t="n">
-        <v>-0.0590969876219888</v>
+        <v>0.1115118150477062</v>
       </c>
       <c r="FI19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ19" t="n">
         <v>-0</v>
       </c>
       <c r="FK19" t="n">
-        <v>0.06317655705183579</v>
+        <v>-0.2155954427000649</v>
       </c>
       <c r="FL19" t="n">
         <v>-0</v>
       </c>
       <c r="FM19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO19" t="n">
         <v>0</v>
       </c>
       <c r="FP19" t="n">
-        <v>-0.02912566105188834</v>
+        <v>0.06268744393611676</v>
       </c>
       <c r="FQ19" t="n">
-        <v>-0.04646807916857813</v>
+        <v>-0.09401824395436371</v>
       </c>
       <c r="FR19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS19" t="n">
         <v>-0</v>
       </c>
       <c r="FT19" t="n">
-        <v>-0.07951849866036313</v>
+        <v>0.362114518358682</v>
       </c>
       <c r="FU19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW19" t="n">
         <v>0</v>
@@ -11212,10 +11212,10 @@
         <v>-0</v>
       </c>
       <c r="FY19" t="n">
-        <v>-0.08923344350431392</v>
+        <v>0.08660910443618862</v>
       </c>
       <c r="FZ19" t="n">
-        <v>-0.07314189295924445</v>
+        <v>0.008158603916996104</v>
       </c>
       <c r="GA19" t="n">
         <v>0</v>
@@ -11224,10 +11224,10 @@
         <v>-0</v>
       </c>
       <c r="GC19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE19" t="n">
         <v>-0</v>
